--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="333">
   <si>
     <t/>
   </si>
@@ -418,24 +418,24 @@
     <t>SQ CHUNKY CUPID 3X26</t>
   </si>
   <si>
+    <t>20141063</t>
+  </si>
+  <si>
+    <t>SQ CSHW BTRFLY 3X22G</t>
+  </si>
+  <si>
+    <t>20140185</t>
+  </si>
+  <si>
+    <t>SQ CHUNKY MINIS 10X8</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>TG,(E-1B)</t>
   </si>
   <si>
-    <t>20141063</t>
-  </si>
-  <si>
-    <t>SQ CSHW BTRFLY 3X22G</t>
-  </si>
-  <si>
-    <t>20140185</t>
-  </si>
-  <si>
-    <t>SQ CHUNKY MINIS 10X8</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>20130159</t>
   </si>
   <si>
@@ -586,6 +586,15 @@
     <t>HARIBO HPY COLA 80G</t>
   </si>
   <si>
+    <t>20141955</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY KOR BBQ70</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
     <t>10000312</t>
   </si>
   <si>
@@ -910,13 +919,19 @@
     <t>KOPIKO CANDY PCK 8'S</t>
   </si>
   <si>
+    <t>20141954</t>
+  </si>
+  <si>
+    <t>YUPI CRUNCY GUMMY 50</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>20117684</t>
   </si>
   <si>
     <t>KALPA SHRE IT 90G</t>
-  </si>
-  <si>
-    <t>19</t>
   </si>
   <si>
     <t>20137063</t>
@@ -1387,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2594,15 +2609,15 @@
         <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>135</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2614,27 +2629,27 @@
         <v>21</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>135</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2648,7 +2663,7 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>8</v>
@@ -2668,7 +2683,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>12</v>
@@ -2688,7 +2703,7 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>15</v>
@@ -2708,7 +2723,7 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>18</v>
@@ -2728,7 +2743,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>21</v>
@@ -2748,7 +2763,7 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>24</v>
@@ -2768,7 +2783,7 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>42</v>
@@ -2788,7 +2803,7 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>45</v>
@@ -2808,10 +2823,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3128,13 +3143,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3148,10 +3163,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3159,19 +3174,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3179,19 +3194,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3199,19 +3214,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3219,59 +3234,59 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3279,19 +3294,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3299,19 +3314,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3328,10 +3343,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3339,19 +3354,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3359,19 +3374,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3379,59 +3394,59 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3439,19 +3454,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3459,19 +3474,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3479,19 +3494,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3508,10 +3523,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3519,19 +3534,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3539,19 +3554,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3559,19 +3574,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3579,19 +3594,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3599,19 +3614,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3619,19 +3634,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3648,10 +3663,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3659,39 +3674,39 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>9</v>
@@ -3699,39 +3714,39 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3739,19 +3754,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3759,19 +3774,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3788,10 +3803,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3799,39 +3814,39 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>9</v>
@@ -3839,19 +3854,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>9</v>
@@ -3859,42 +3874,42 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>274</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3908,53 +3923,53 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>277</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>274</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>33</v>
+        <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3968,73 +3983,73 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>274</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4048,30 +4063,30 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>293</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4079,19 +4094,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4099,19 +4114,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4119,19 +4134,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4148,10 +4163,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4159,19 +4174,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4179,19 +4194,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4199,19 +4214,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4219,19 +4234,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4239,19 +4254,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4259,19 +4274,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4279,19 +4294,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4299,19 +4314,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4319,19 +4334,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4339,19 +4354,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4359,41 +4374,81 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>290</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="F150" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="329">
   <si>
     <t/>
   </si>
@@ -334,12 +334,6 @@
     <t>CADBURY HAZELNUT 52G</t>
   </si>
   <si>
-    <t>20054754</t>
-  </si>
-  <si>
-    <t>CADBURY FRUIT&amp;NUT 30</t>
-  </si>
-  <si>
     <t>20134029</t>
   </si>
   <si>
@@ -356,12 +350,6 @@
   </si>
   <si>
     <t>KINDER JOY DC COMICS</t>
-  </si>
-  <si>
-    <t>20141135</t>
-  </si>
-  <si>
-    <t>DARK WNDR ALMD 2X56G</t>
   </si>
   <si>
     <t>20133639</t>
@@ -1402,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2346,7 +2334,7 @@
         <v>24</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2366,7 +2354,7 @@
         <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2386,7 +2374,7 @@
         <v>24</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2403,10 +2391,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2426,7 +2414,7 @@
         <v>42</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2446,7 +2434,7 @@
         <v>42</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2466,7 +2454,7 @@
         <v>42</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2483,10 +2471,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2503,10 +2491,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2526,7 +2514,7 @@
         <v>45</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2546,7 +2534,7 @@
         <v>45</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2566,7 +2554,7 @@
         <v>45</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2586,7 +2574,7 @@
         <v>45</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2603,30 +2591,30 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2634,22 +2622,22 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>140</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2663,13 +2651,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2683,13 +2671,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2703,10 +2691,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>74</v>
@@ -2723,10 +2711,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>74</v>
@@ -2743,13 +2731,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2763,13 +2751,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2783,13 +2771,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2803,10 +2791,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2814,39 +2802,39 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="E71" s="1" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2863,13 +2851,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2883,10 +2871,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2903,10 +2891,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2923,13 +2911,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2943,10 +2931,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2954,39 +2942,39 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3003,10 +2991,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3023,10 +3011,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3043,10 +3031,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3063,10 +3051,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3083,10 +3071,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3103,30 +3091,30 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3134,39 +3122,39 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3183,10 +3171,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3203,10 +3191,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3223,13 +3211,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3243,10 +3231,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3263,13 +3251,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3283,10 +3271,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3303,10 +3291,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3314,19 +3302,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3334,19 +3322,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3363,10 +3351,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3383,13 +3371,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3403,10 +3391,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3423,13 +3411,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3443,10 +3431,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3463,10 +3451,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3483,10 +3471,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3494,19 +3482,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3514,19 +3502,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3543,10 +3531,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3563,10 +3551,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3583,10 +3571,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3603,10 +3591,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3623,10 +3611,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3634,19 +3622,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3654,22 +3642,22 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3683,13 +3671,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3703,13 +3691,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3723,13 +3711,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3743,10 +3731,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3763,10 +3751,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3774,19 +3762,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3794,22 +3782,22 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3823,13 +3811,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3843,10 +3831,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>9</v>
@@ -3863,13 +3851,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3883,30 +3871,30 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3914,22 +3902,22 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3943,53 +3931,53 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4003,13 +3991,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4023,53 +4011,53 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>9</v>
+        <v>289</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>293</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4083,10 +4071,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4103,10 +4091,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4123,10 +4111,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4134,19 +4122,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4154,19 +4142,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4183,10 +4171,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4203,10 +4191,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4223,10 +4211,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4243,10 +4231,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4263,10 +4251,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4283,10 +4271,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4303,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4323,10 +4311,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4343,10 +4331,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4363,10 +4351,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4383,13 +4371,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>289</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4403,52 +4391,12 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F152" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -151,6 +151,15 @@
     <t>9</t>
   </si>
   <si>
+    <t>20083719</t>
+  </si>
+  <si>
+    <t>NANO MILKY COK 12G</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20033392</t>
   </si>
   <si>
@@ -181,340 +190,742 @@
     <t>M&amp;M'S CHOC CRSPY 30G</t>
   </si>
   <si>
+    <t>20129814</t>
+  </si>
+  <si>
+    <t>MLKITA CNDY BTES 24G</t>
+  </si>
+  <si>
+    <t>20140908</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD STRW 85G</t>
+  </si>
+  <si>
+    <t>20140907</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD MILK 85G</t>
+  </si>
+  <si>
+    <t>20045175</t>
+  </si>
+  <si>
+    <t>CHA CHA MILK CHO 20G</t>
+  </si>
+  <si>
+    <t>20045176</t>
+  </si>
+  <si>
+    <t>CHA CHA PNUT CHO 20G</t>
+  </si>
+  <si>
+    <t>20063093</t>
+  </si>
+  <si>
+    <t>DELFI MALTITOS 26</t>
+  </si>
+  <si>
+    <t>10000418</t>
+  </si>
+  <si>
+    <t>DELFI CHIC CHOC 36G</t>
+  </si>
+  <si>
+    <t>20024539</t>
+  </si>
+  <si>
+    <t>S/Q BITES ALMOND 30G</t>
+  </si>
+  <si>
+    <t>20128815</t>
+  </si>
+  <si>
+    <t>IDM GUMMY CHO MF 40G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140906</t>
+  </si>
+  <si>
+    <t>MILKITA BAR CHOC 15G</t>
+  </si>
+  <si>
+    <t>20140412</t>
+  </si>
+  <si>
+    <t>MILKITA MILKY BAR 15</t>
+  </si>
+  <si>
+    <t>20113490</t>
+  </si>
+  <si>
+    <t>BENG-BENG ALMOND 35G</t>
+  </si>
+  <si>
+    <t>20044008</t>
+  </si>
+  <si>
+    <t>BENG-BENG MAXX 32G</t>
+  </si>
+  <si>
+    <t>20117108</t>
+  </si>
+  <si>
+    <t>BENG-BENG PCK 3X20G</t>
+  </si>
+  <si>
+    <t>20112348</t>
+  </si>
+  <si>
+    <t>IDM BLUEBRY D.CHO 45</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20085730</t>
+  </si>
+  <si>
+    <t>IDM CASH MILK CHO 40</t>
+  </si>
+  <si>
+    <t>20093638</t>
+  </si>
+  <si>
+    <t>IDM BISC MILK CHO 40</t>
+  </si>
+  <si>
+    <t>20046198</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCOLAT 51</t>
+  </si>
+  <si>
+    <t>20011878</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCO 35G</t>
+  </si>
+  <si>
+    <t>10008315</t>
+  </si>
+  <si>
+    <t>KINDER BUENO CHO 43G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20139949</t>
+  </si>
+  <si>
+    <t>LMNILO CRNCHY CHO 18</t>
+  </si>
+  <si>
+    <t>20134029</t>
+  </si>
+  <si>
+    <t>DELFI TRSURE MLK2X30</t>
+  </si>
+  <si>
+    <t>20130547</t>
+  </si>
+  <si>
+    <t>DELFI CHOCO DM 2X25G</t>
+  </si>
+  <si>
+    <t>10000757</t>
+  </si>
+  <si>
+    <t>L'AGIE FULL MILK 60G</t>
+  </si>
+  <si>
+    <t>20120946</t>
+  </si>
+  <si>
+    <t>KINDER JOY DC COMICS</t>
+  </si>
+  <si>
+    <t>20133639</t>
+  </si>
+  <si>
+    <t>DW DARK.CHO ALMND 56</t>
+  </si>
+  <si>
+    <t>20089666</t>
+  </si>
+  <si>
+    <t>CADBURY CSHW NUT 85G</t>
+  </si>
+  <si>
+    <t>20062877</t>
+  </si>
+  <si>
+    <t>CADBURY BLCK.FOR 57G</t>
+  </si>
+  <si>
+    <t>20054753</t>
+  </si>
+  <si>
+    <t>CADBURY FRUIT&amp;NUT 52</t>
+  </si>
+  <si>
+    <t>20120257</t>
+  </si>
+  <si>
+    <t>CADBURY HAZELNUT 52G</t>
+  </si>
+  <si>
+    <t>20140883</t>
+  </si>
+  <si>
+    <t>CADBURY BUBBLY 46G</t>
+  </si>
+  <si>
+    <t>20141062</t>
+  </si>
+  <si>
+    <t>SQ CHUNKY CUPID 3X26</t>
+  </si>
+  <si>
+    <t>20141063</t>
+  </si>
+  <si>
+    <t>SQ CSHW BTRFLY 3X22G</t>
+  </si>
+  <si>
+    <t>20008798</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY CASHEW 82</t>
+  </si>
+  <si>
+    <t>10036987</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHEW 52G</t>
+  </si>
+  <si>
+    <t>20092545</t>
+  </si>
+  <si>
+    <t>SLVR QUEEN MATCHA 52</t>
+  </si>
+  <si>
+    <t>20092546</t>
+  </si>
+  <si>
+    <t>SLVR QUEEN MATCHA 22</t>
+  </si>
+  <si>
+    <t>20140185</t>
+  </si>
+  <si>
+    <t>SQ CHUNKY MINIS 10X8</t>
+  </si>
+  <si>
+    <t>TG,(E-1B)</t>
+  </si>
+  <si>
+    <t>20130159</t>
+  </si>
+  <si>
+    <t>CADBURY SHAREBAG 81G</t>
+  </si>
+  <si>
+    <t>20141835</t>
+  </si>
+  <si>
+    <t>CADBURY OREO SHRBAG</t>
+  </si>
+  <si>
+    <t>20137070</t>
+  </si>
+  <si>
+    <t>MILO CHOCO CUBE67.5G</t>
+  </si>
+  <si>
+    <t>20129560</t>
+  </si>
+  <si>
+    <t>IDM HAZEL CHOCO 60G</t>
+  </si>
+  <si>
+    <t>20129562</t>
+  </si>
+  <si>
+    <t>IDM FD STRW CHOC 45G</t>
+  </si>
+  <si>
+    <t>20129561</t>
+  </si>
+  <si>
+    <t>IDM RAISIN CHOCO 60G</t>
+  </si>
+  <si>
+    <t>20129559</t>
+  </si>
+  <si>
+    <t>IDM ALMND CHOCO 60G</t>
+  </si>
+  <si>
+    <t>20093135</t>
+  </si>
+  <si>
+    <t>BENG-BENG SHR IT 10S</t>
+  </si>
+  <si>
+    <t>20115505</t>
+  </si>
+  <si>
+    <t>DILAN CHOCO CRML 95G</t>
+  </si>
+  <si>
+    <t>20117684</t>
+  </si>
+  <si>
+    <t>KALPA SHRE IT 90G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20053360</t>
+  </si>
+  <si>
+    <t>ALPNLIEBE ECLRS 126G</t>
+  </si>
+  <si>
+    <t>10037013</t>
+  </si>
+  <si>
+    <t>RELAXA BARLEY MNT108</t>
+  </si>
+  <si>
+    <t>20043035</t>
+  </si>
+  <si>
+    <t>H/WHITE GUM MINT 70G</t>
+  </si>
+  <si>
+    <t>10012263</t>
+  </si>
+  <si>
+    <t>TAMARIN CDY ASEM 81G</t>
+  </si>
+  <si>
+    <t>20024096</t>
+  </si>
+  <si>
+    <t>KIS CND MNT GRAPE 75</t>
+  </si>
+  <si>
+    <t>10000172</t>
+  </si>
+  <si>
+    <t>KOPIKO CANDY PCK 105</t>
+  </si>
+  <si>
+    <t>20040504</t>
+  </si>
+  <si>
+    <t>MILKITA CANDY 12'S</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20077302</t>
+  </si>
+  <si>
+    <t>MILKITA CANDY MLK30S</t>
+  </si>
+  <si>
+    <t>20127602</t>
+  </si>
+  <si>
+    <t>SZ CANDY ASSTRD 50S</t>
+  </si>
+  <si>
+    <t>10002564</t>
+  </si>
+  <si>
+    <t>MENTOS MINT 121.5GR</t>
+  </si>
+  <si>
+    <t>10030199</t>
+  </si>
+  <si>
+    <t>MNTOS CND BUAH 121.5</t>
+  </si>
+  <si>
+    <t>20028732</t>
+  </si>
+  <si>
+    <t>MINTZ CDY.DUO MNT 99</t>
+  </si>
+  <si>
+    <t>20031736</t>
+  </si>
+  <si>
+    <t>MINTZ CNDY.PPRMNT 99</t>
+  </si>
+  <si>
+    <t>20136282</t>
+  </si>
+  <si>
+    <t>MILKITA LOLIPOP 3'S</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20082651</t>
+  </si>
+  <si>
+    <t>BIG BB FLFLY TTFR 11</t>
+  </si>
+  <si>
+    <t>20113106</t>
+  </si>
+  <si>
+    <t>YUPI SWT ARTIFACT 77</t>
+  </si>
+  <si>
+    <t>10013885</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY LUNCH 93</t>
+  </si>
+  <si>
+    <t>10008620</t>
+  </si>
+  <si>
+    <t>YUPI MINI BURGER 105</t>
+  </si>
+  <si>
+    <t>20079510</t>
+  </si>
+  <si>
+    <t>YUPI BREAKFAST 95G</t>
+  </si>
+  <si>
+    <t>10006539</t>
+  </si>
+  <si>
+    <t>YUPI KISS STRAW 110G</t>
+  </si>
+  <si>
+    <t>20140015</t>
+  </si>
+  <si>
+    <t>AMOS BANANA GUMMY 68</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20141597</t>
+  </si>
+  <si>
+    <t>FRUZZ GUMMY ASORTD36</t>
+  </si>
+  <si>
+    <t>20138897</t>
+  </si>
+  <si>
+    <t>JLO FRIED EGG 78G</t>
+  </si>
+  <si>
+    <t>20129720</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY WLD SFR44</t>
+  </si>
+  <si>
+    <t>10000312</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY GL.STK 45</t>
+  </si>
+  <si>
+    <t>10006540</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY BB.BEAR45</t>
+  </si>
+  <si>
+    <t>20064920</t>
+  </si>
+  <si>
+    <t>YUPI LITTLE STARS 45</t>
+  </si>
+  <si>
+    <t>20141954</t>
+  </si>
+  <si>
+    <t>YUPI CRUNCY GUMMY 50</t>
+  </si>
+  <si>
+    <t>20139394</t>
+  </si>
+  <si>
+    <t>JLO GUMMY BEAR 40G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20135995</t>
+  </si>
+  <si>
+    <t>JLO GUMMY BITE 40G</t>
+  </si>
+  <si>
+    <t>20087289</t>
+  </si>
+  <si>
+    <t>CHP.CHUPS BITES 56G</t>
+  </si>
+  <si>
+    <t>20139774</t>
+  </si>
+  <si>
+    <t>CH.CHUP ROPES S/C 24</t>
+  </si>
+  <si>
+    <t>10006534</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY KS.STW 45</t>
+  </si>
+  <si>
+    <t>20080530</t>
+  </si>
+  <si>
+    <t>YUPI BIG BURGER 32G</t>
+  </si>
+  <si>
+    <t>20048724</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY PIZZA 23G</t>
+  </si>
+  <si>
+    <t>20136191</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY NOODLE23G</t>
+  </si>
+  <si>
+    <t>20052776</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY B/FRNK 32</t>
+  </si>
+  <si>
+    <t>20047250</t>
+  </si>
+  <si>
+    <t>YUPI CALCI BEAN 70G</t>
+  </si>
+  <si>
     <t>20138164</t>
   </si>
   <si>
     <t>AMOS GUMMY RBT  72G</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20125849</t>
   </si>
   <si>
     <t>AMOS GUMMY 4D BLK 72</t>
   </si>
   <si>
-    <t>20140015</t>
-  </si>
-  <si>
-    <t>AMOS BANANA GUMMY 68</t>
-  </si>
-  <si>
-    <t>20045175</t>
-  </si>
-  <si>
-    <t>CHA CHA MILK CHO 20G</t>
-  </si>
-  <si>
-    <t>20045176</t>
-  </si>
-  <si>
-    <t>CHA CHA PNUT CHO 20G</t>
-  </si>
-  <si>
-    <t>20063093</t>
-  </si>
-  <si>
-    <t>DELFI MALTITOS 26</t>
-  </si>
-  <si>
-    <t>10000418</t>
-  </si>
-  <si>
-    <t>DELFI CHIC CHOC 36G</t>
-  </si>
-  <si>
-    <t>20024539</t>
-  </si>
-  <si>
-    <t>S/Q BITES ALMOND 30G</t>
-  </si>
-  <si>
-    <t>20128815</t>
-  </si>
-  <si>
-    <t>IDM GUMMY CHO MF 40G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140906</t>
-  </si>
-  <si>
-    <t>MILKITA BAR CHOC 15G</t>
-  </si>
-  <si>
-    <t>20140412</t>
-  </si>
-  <si>
-    <t>MILKITA MILKY BAR 15</t>
-  </si>
-  <si>
-    <t>20139949</t>
-  </si>
-  <si>
-    <t>LMNILO CRNCHY CHO 18</t>
-  </si>
-  <si>
-    <t>20113490</t>
-  </si>
-  <si>
-    <t>BENG-BENG ALMOND 35G</t>
-  </si>
-  <si>
-    <t>20044008</t>
-  </si>
-  <si>
-    <t>BENG-BENG MAXX 32G</t>
-  </si>
-  <si>
-    <t>20117108</t>
-  </si>
-  <si>
-    <t>BENG-BENG PCK 3X20G</t>
-  </si>
-  <si>
-    <t>20112348</t>
-  </si>
-  <si>
-    <t>IDM BLUEBRY D.CHO 45</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20085730</t>
-  </si>
-  <si>
-    <t>IDM CASH MILK CHO 40</t>
-  </si>
-  <si>
-    <t>20093638</t>
-  </si>
-  <si>
-    <t>IDM BISC MILK CHO 40</t>
-  </si>
-  <si>
-    <t>10008315</t>
-  </si>
-  <si>
-    <t>KINDER BUENO CHO 43G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20046198</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCOLAT 51</t>
-  </si>
-  <si>
-    <t>20011878</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCO 35G</t>
-  </si>
-  <si>
-    <t>10000757</t>
-  </si>
-  <si>
-    <t>L'AGIE FULL MILK 60G</t>
-  </si>
-  <si>
-    <t>20054753</t>
-  </si>
-  <si>
-    <t>CADBURY FRUIT&amp;NUT 52</t>
-  </si>
-  <si>
-    <t>20120257</t>
-  </si>
-  <si>
-    <t>CADBURY HAZELNUT 52G</t>
-  </si>
-  <si>
-    <t>20134029</t>
-  </si>
-  <si>
-    <t>DELFI TRSURE MLK2X30</t>
-  </si>
-  <si>
-    <t>20130547</t>
-  </si>
-  <si>
-    <t>DELFI CHOCO DM 2X25G</t>
-  </si>
-  <si>
-    <t>20120946</t>
-  </si>
-  <si>
-    <t>KINDER JOY DC COMICS</t>
-  </si>
-  <si>
-    <t>20133639</t>
-  </si>
-  <si>
-    <t>DW DARK.CHO ALMND 56</t>
-  </si>
-  <si>
-    <t>20089666</t>
-  </si>
-  <si>
-    <t>CADBURY CSHW NUT 85G</t>
-  </si>
-  <si>
-    <t>20062877</t>
-  </si>
-  <si>
-    <t>CADBURY BLCK.FOR 57G</t>
-  </si>
-  <si>
-    <t>20140883</t>
-  </si>
-  <si>
-    <t>CADBURY BUBBLY 46G</t>
-  </si>
-  <si>
-    <t>20008798</t>
-  </si>
-  <si>
-    <t>S/Q CHUNKY CASHEW 82</t>
-  </si>
-  <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
-  </si>
-  <si>
-    <t>20092545</t>
-  </si>
-  <si>
-    <t>SLVR QUEEN MATCHA 52</t>
-  </si>
-  <si>
-    <t>20092546</t>
-  </si>
-  <si>
-    <t>SLVR QUEEN MATCHA 22</t>
-  </si>
-  <si>
-    <t>20141062</t>
-  </si>
-  <si>
-    <t>SQ CHUNKY CUPID 3X26</t>
-  </si>
-  <si>
-    <t>20141063</t>
-  </si>
-  <si>
-    <t>SQ CSHW BTRFLY 3X22G</t>
-  </si>
-  <si>
-    <t>20140185</t>
-  </si>
-  <si>
-    <t>SQ CHUNKY MINIS 10X8</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
-    <t>20130159</t>
-  </si>
-  <si>
-    <t>CADBURY SHAREBAG 81G</t>
-  </si>
-  <si>
-    <t>20137070</t>
-  </si>
-  <si>
-    <t>MILO CHOCO CUBE67.5G</t>
-  </si>
-  <si>
-    <t>20129560</t>
-  </si>
-  <si>
-    <t>IDM HAZEL CHOCO 60G</t>
-  </si>
-  <si>
-    <t>20129562</t>
-  </si>
-  <si>
-    <t>IDM FD STRW CHOC 45G</t>
-  </si>
-  <si>
-    <t>20129561</t>
-  </si>
-  <si>
-    <t>IDM RAISIN CHOCO 60G</t>
-  </si>
-  <si>
-    <t>20129559</t>
-  </si>
-  <si>
-    <t>IDM ALMND CHOCO 60G</t>
-  </si>
-  <si>
-    <t>20115505</t>
-  </si>
-  <si>
-    <t>DILAN CHOCO CRML 95G</t>
-  </si>
-  <si>
-    <t>20093135</t>
-  </si>
-  <si>
-    <t>BENG-BENG SHR IT 10S</t>
-  </si>
-  <si>
-    <t>20141835</t>
-  </si>
-  <si>
-    <t>CADBURY OREO SHRBAG</t>
-  </si>
-  <si>
-    <t>20138897</t>
-  </si>
-  <si>
-    <t>JLO FRIED EGG 78G</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20113106</t>
-  </si>
-  <si>
-    <t>YUPI SWT ARTIFACT 77</t>
-  </si>
-  <si>
-    <t>10013885</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY LUNCH 93</t>
-  </si>
-  <si>
-    <t>10008620</t>
-  </si>
-  <si>
-    <t>YUPI MINI BURGER 105</t>
-  </si>
-  <si>
-    <t>20079510</t>
-  </si>
-  <si>
-    <t>YUPI BREAKFAST 95G</t>
-  </si>
-  <si>
-    <t>10006539</t>
-  </si>
-  <si>
-    <t>YUPI KISS STRAW 110G</t>
+    <t>20137885</t>
+  </si>
+  <si>
+    <t>CHUPA JELY OCEAN FUN</t>
+  </si>
+  <si>
+    <t>20137884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHUPA JELLY FUN MIX </t>
+  </si>
+  <si>
+    <t>20049229</t>
+  </si>
+  <si>
+    <t>HARIBO GLD BEARS 80</t>
+  </si>
+  <si>
+    <t>20049227</t>
+  </si>
+  <si>
+    <t>HARIBO HPY COLA 80G</t>
+  </si>
+  <si>
+    <t>20139685</t>
+  </si>
+  <si>
+    <t>BONCHA GUMMY BLND 30</t>
+  </si>
+  <si>
+    <t>20141955</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY KOR BBQ70</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>10000766</t>
+  </si>
+  <si>
+    <t>SUGUS STICK STB30GR</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>10000765</t>
+  </si>
+  <si>
+    <t>SUGUS STICK BLCRNT30</t>
+  </si>
+  <si>
+    <t>20014081</t>
+  </si>
+  <si>
+    <t>FROZZ CND BLUBERYT15</t>
+  </si>
+  <si>
+    <t>10003481</t>
+  </si>
+  <si>
+    <t>FROZZ BARLEY MINT 15</t>
+  </si>
+  <si>
+    <t>10003491</t>
+  </si>
+  <si>
+    <t>FROZZ CHERRY MINT 15</t>
+  </si>
+  <si>
+    <t>20138041</t>
+  </si>
+  <si>
+    <t>FROZZ MANGO BINGSO14</t>
+  </si>
+  <si>
+    <t>20067474</t>
+  </si>
+  <si>
+    <t>CAPUNG PASTILLES 7G</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20121168</t>
+  </si>
+  <si>
+    <t>RICOLA LEMON MINT 40</t>
+  </si>
+  <si>
+    <t>20121182</t>
+  </si>
+  <si>
+    <t>RICOLA GLACIER FM 40</t>
+  </si>
+  <si>
+    <t>20002898</t>
+  </si>
+  <si>
+    <t>GO FRESS PRMINT 24'S</t>
+  </si>
+  <si>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20133371</t>
+  </si>
+  <si>
+    <t>MLTON PSTL BCRNT16.5</t>
+  </si>
+  <si>
+    <t>20133370</t>
+  </si>
+  <si>
+    <t>MILTON PSTLS LMN16.5</t>
+  </si>
+  <si>
+    <t>20099973</t>
+  </si>
+  <si>
+    <t>HMLYA SL CNDY LMN 15</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20109048</t>
+  </si>
+  <si>
+    <t>HEXOS MINT 8'S</t>
+  </si>
+  <si>
+    <t>10011038</t>
+  </si>
+  <si>
+    <t>WOODS PEP.EXT/STRG15</t>
+  </si>
+  <si>
+    <t>10033024</t>
+  </si>
+  <si>
+    <t>S/M CANDY TLK.AGN 5S</t>
+  </si>
+  <si>
+    <t>20110265</t>
+  </si>
+  <si>
+    <t>KOPIKO S/FREE CNDY32</t>
+  </si>
+  <si>
+    <t>20101063</t>
+  </si>
+  <si>
+    <t>KOPIKO CANDY PCK 8'S</t>
+  </si>
+  <si>
+    <t>20140413</t>
+  </si>
+  <si>
+    <t>SUPER ZUPER  PCK 5S</t>
+  </si>
+  <si>
+    <t>20138030</t>
+  </si>
+  <si>
+    <t>JGOAN/N LOLY LDH WRN</t>
+  </si>
+  <si>
+    <t>20137064</t>
+  </si>
+  <si>
+    <t>IDM CND GUMMY PUZL50</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>20137681</t>
@@ -523,316 +934,10 @@
     <t>IDM GUMMY STRW MGO50</t>
   </si>
   <si>
-    <t>10006534</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY KS.STW 45</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20064920</t>
-  </si>
-  <si>
-    <t>YUPI LITTLE STARS 45</t>
-  </si>
-  <si>
-    <t>20137885</t>
-  </si>
-  <si>
-    <t>CHUPA JELY OCEAN FUN</t>
-  </si>
-  <si>
-    <t>20137884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHUPA JELLY FUN MIX </t>
-  </si>
-  <si>
-    <t>20139774</t>
-  </si>
-  <si>
-    <t>CH.CHUP ROPES S/C 24</t>
-  </si>
-  <si>
-    <t>20087289</t>
-  </si>
-  <si>
-    <t>CHP.CHUPS BITES 56G</t>
-  </si>
-  <si>
-    <t>20049229</t>
-  </si>
-  <si>
-    <t>HARIBO GLD BEARS 80</t>
-  </si>
-  <si>
-    <t>20049227</t>
-  </si>
-  <si>
-    <t>HARIBO HPY COLA 80G</t>
-  </si>
-  <si>
-    <t>20141955</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY KOR BBQ70</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
-    <t>10000312</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY GL.STK 45</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10006540</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY BB.BEAR45</t>
-  </si>
-  <si>
-    <t>20129720</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY WLD SFR44</t>
-  </si>
-  <si>
-    <t>20080530</t>
-  </si>
-  <si>
-    <t>YUPI BIG BURGER 32G</t>
-  </si>
-  <si>
-    <t>20048724</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY PIZZA 23G</t>
-  </si>
-  <si>
-    <t>20136191</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY NOODLE23G</t>
-  </si>
-  <si>
-    <t>20047250</t>
-  </si>
-  <si>
-    <t>YUPI CALCI BEAN 70G</t>
-  </si>
-  <si>
-    <t>20052776</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY B/FRNK 32</t>
-  </si>
-  <si>
-    <t>20137064</t>
-  </si>
-  <si>
-    <t>IDM CND GUMMY PUZL50</t>
-  </si>
-  <si>
-    <t>20140907</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD MILK 85G</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20140908</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD STRW 85G</t>
-  </si>
-  <si>
-    <t>20129814</t>
-  </si>
-  <si>
-    <t>MLKITA CNDY BTES 24G</t>
-  </si>
-  <si>
-    <t>20082651</t>
-  </si>
-  <si>
-    <t>BIG BB FLFLY TTFR 11</t>
-  </si>
-  <si>
-    <t>20083719</t>
-  </si>
-  <si>
-    <t>NANO MILKY COK 12G</t>
-  </si>
-  <si>
-    <t>20138030</t>
-  </si>
-  <si>
-    <t>JGOAN/N LOLY LDH WRN</t>
-  </si>
-  <si>
-    <t>20139394</t>
-  </si>
-  <si>
-    <t>JLO GUMMY BEAR 40G</t>
-  </si>
-  <si>
-    <t>20139685</t>
-  </si>
-  <si>
-    <t>BONCHA GUMMY BLND 30</t>
-  </si>
-  <si>
-    <t>20135995</t>
-  </si>
-  <si>
-    <t>JLO GUMMY BITE 40G</t>
-  </si>
-  <si>
-    <t>20053360</t>
-  </si>
-  <si>
-    <t>ALPNLIEBE ECLRS 126G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>10012263</t>
-  </si>
-  <si>
-    <t>TAMARIN CDY ASEM 81G</t>
-  </si>
-  <si>
-    <t>20024096</t>
-  </si>
-  <si>
-    <t>KIS CND MNT GRAPE 75</t>
-  </si>
-  <si>
-    <t>10037013</t>
-  </si>
-  <si>
-    <t>RELAXA BARLEY MNT108</t>
-  </si>
-  <si>
-    <t>20040504</t>
-  </si>
-  <si>
-    <t>MILKITA CANDY 12'S</t>
-  </si>
-  <si>
-    <t>20077302</t>
-  </si>
-  <si>
-    <t>MILKITA CANDY MLK30S</t>
-  </si>
-  <si>
-    <t>20136282</t>
-  </si>
-  <si>
-    <t>MILKITA LOLIPOP 3'S</t>
-  </si>
-  <si>
-    <t>10002564</t>
-  </si>
-  <si>
-    <t>MENTOS MINT 121.5GR</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>10030199</t>
-  </si>
-  <si>
-    <t>MNTOS CND BUAH 121.5</t>
-  </si>
-  <si>
-    <t>20031736</t>
-  </si>
-  <si>
-    <t>MINTZ CNDY.PPRMNT 99</t>
-  </si>
-  <si>
-    <t>20028732</t>
-  </si>
-  <si>
-    <t>MINTZ CDY.DUO MNT 99</t>
-  </si>
-  <si>
-    <t>20043035</t>
-  </si>
-  <si>
-    <t>H/WHITE GUM MINT 70G</t>
-  </si>
-  <si>
-    <t>20127602</t>
-  </si>
-  <si>
-    <t>SZ CANDY ASSTRD 50S</t>
-  </si>
-  <si>
-    <t>10000172</t>
-  </si>
-  <si>
-    <t>KOPIKO CANDY PCK 105</t>
-  </si>
-  <si>
-    <t>10000766</t>
-  </si>
-  <si>
-    <t>SUGUS STICK STB30GR</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>10000765</t>
-  </si>
-  <si>
-    <t>SUGUS STICK BLCRNT30</t>
-  </si>
-  <si>
-    <t>20014081</t>
-  </si>
-  <si>
-    <t>FROZZ CND BLUBERYT15</t>
-  </si>
-  <si>
-    <t>10003481</t>
-  </si>
-  <si>
-    <t>FROZZ BARLEY MINT 15</t>
-  </si>
-  <si>
-    <t>10003491</t>
-  </si>
-  <si>
-    <t>FROZZ CHERRY MINT 15</t>
-  </si>
-  <si>
-    <t>20138041</t>
-  </si>
-  <si>
-    <t>FROZZ MANGO BINGSO14</t>
-  </si>
-  <si>
-    <t>20067474</t>
-  </si>
-  <si>
-    <t>CAPUNG PASTILLES 7G</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
+    <t>20137063</t>
+  </si>
+  <si>
+    <t>IDM CND GUMMY ORG88G</t>
   </si>
   <si>
     <t>20016240</t>
@@ -847,87 +952,6 @@
     <t>FOX'S CANDY FRUIT 90</t>
   </si>
   <si>
-    <t>20099973</t>
-  </si>
-  <si>
-    <t>HMLYA SL CNDY LMN 15</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20140413</t>
-  </si>
-  <si>
-    <t>SUPER ZUPER  PCK 5S</t>
-  </si>
-  <si>
-    <t>20109048</t>
-  </si>
-  <si>
-    <t>HEXOS MINT 8'S</t>
-  </si>
-  <si>
-    <t>10011038</t>
-  </si>
-  <si>
-    <t>WOODS PEP.EXT/STRG15</t>
-  </si>
-  <si>
-    <t>10033024</t>
-  </si>
-  <si>
-    <t>S/M CANDY TLK.AGN 5S</t>
-  </si>
-  <si>
-    <t>RT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20133371</t>
-  </si>
-  <si>
-    <t>MLTON PSTL BCRNT16.5</t>
-  </si>
-  <si>
-    <t>20133370</t>
-  </si>
-  <si>
-    <t>MILTON PSTLS LMN16.5</t>
-  </si>
-  <si>
-    <t>20110265</t>
-  </si>
-  <si>
-    <t>KOPIKO S/FREE CNDY32</t>
-  </si>
-  <si>
-    <t>20101063</t>
-  </si>
-  <si>
-    <t>KOPIKO CANDY PCK 8'S</t>
-  </si>
-  <si>
-    <t>20141954</t>
-  </si>
-  <si>
-    <t>YUPI CRUNCY GUMMY 50</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20117684</t>
-  </si>
-  <si>
-    <t>KALPA SHRE IT 90G</t>
-  </si>
-  <si>
-    <t>20137063</t>
-  </si>
-  <si>
-    <t>IDM CND GUMMY ORG88G</t>
-  </si>
-  <si>
     <t>10028390</t>
   </si>
   <si>
@@ -974,30 +998,6 @@
   </si>
   <si>
     <t>LOTTE XYLTL BLU26.1</t>
-  </si>
-  <si>
-    <t>20121168</t>
-  </si>
-  <si>
-    <t>RICOLA LEMON MINT 40</t>
-  </si>
-  <si>
-    <t>20121182</t>
-  </si>
-  <si>
-    <t>RICOLA GLACIER FM 40</t>
-  </si>
-  <si>
-    <t>20002898</t>
-  </si>
-  <si>
-    <t>GO FRESS PRMINT 24'S</t>
-  </si>
-  <si>
-    <t>20141597</t>
-  </si>
-  <si>
-    <t>FRUZZ GUMMY ASORTD36</t>
   </si>
 </sst>
 </file>
@@ -1751,21 +1751,21 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1774,7 +1774,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1794,7 +1794,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1834,7 +1834,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1854,7 +1854,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1874,7 +1874,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1882,10 +1882,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1894,7 +1894,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1902,19 +1902,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1934,7 +1934,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1942,10 +1942,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1954,7 +1954,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2017,7 +2017,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2037,15 +2037,15 @@
         <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2142,10 +2142,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2157,15 +2157,15 @@
         <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2177,15 +2177,15 @@
         <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2197,15 +2197,15 @@
         <v>12</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2217,7 +2217,7 @@
         <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2257,15 +2257,15 @@
         <v>21</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2277,15 +2277,15 @@
         <v>24</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2294,7 +2294,7 @@
         <v>24</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2314,7 +2314,7 @@
         <v>24</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2334,18 +2334,18 @@
         <v>24</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2354,7 +2354,7 @@
         <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2362,19 +2362,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2462,19 +2462,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2494,7 +2494,7 @@
         <v>45</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2514,7 +2514,7 @@
         <v>45</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2534,7 +2534,7 @@
         <v>45</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2554,7 +2554,7 @@
         <v>45</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2574,7 +2574,7 @@
         <v>45</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2582,42 +2582,42 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>136</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2631,10 +2631,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2651,13 +2651,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2671,13 +2671,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2691,13 +2691,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2711,13 +2711,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2731,13 +2731,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2751,13 +2751,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2771,10 +2771,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2791,33 +2791,33 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2831,10 +2831,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2851,10 +2851,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2871,10 +2871,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2891,10 +2891,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2911,13 +2911,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2931,10 +2931,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2942,19 +2942,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2971,10 +2971,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2991,10 +2991,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3011,10 +3011,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3031,10 +3031,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3051,13 +3051,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3071,13 +3071,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3091,13 +3091,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>189</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3111,10 +3111,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3122,36 +3122,36 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>15</v>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>18</v>
@@ -3182,16 +3182,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>21</v>
@@ -3202,39 +3202,39 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3251,10 +3251,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3271,10 +3271,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3291,10 +3291,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3302,19 +3302,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3322,19 +3322,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3342,19 +3342,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3362,39 +3362,39 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3411,10 +3411,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3431,10 +3431,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3451,10 +3451,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3471,10 +3471,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3482,19 +3482,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3502,19 +3502,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3522,39 +3522,39 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3562,19 +3562,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3582,19 +3582,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3611,10 +3611,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3622,19 +3622,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3642,59 +3642,59 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3702,19 +3702,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3722,22 +3722,22 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3917,7 +3917,7 @@
         <v>45</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3931,13 +3931,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3951,10 +3951,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3971,13 +3971,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3991,33 +3991,33 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>273</v>
+        <v>33</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>289</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4031,13 +4031,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4051,13 +4051,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4071,10 +4071,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4091,10 +4091,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4111,10 +4111,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4122,19 +4122,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4142,19 +4142,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4171,13 +4171,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4191,10 +4191,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4211,10 +4211,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4231,13 +4231,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4251,10 +4251,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4271,10 +4271,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4291,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4311,10 +4311,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4331,10 +4331,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4351,10 +4351,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4371,13 +4371,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>289</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4391,10 +4391,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="330">
   <si>
     <t/>
   </si>
@@ -511,6 +511,12 @@
     <t>H/WHITE GUM MINT 70G</t>
   </si>
   <si>
+    <t>10032611</t>
+  </si>
+  <si>
+    <t>GARUDA TING2 KCNG125</t>
+  </si>
+  <si>
     <t>10012263</t>
   </si>
   <si>
@@ -628,6 +634,12 @@
     <t>14</t>
   </si>
   <si>
+    <t>20141954</t>
+  </si>
+  <si>
+    <t>YUPI CRUNCY GUMMY 50</t>
+  </si>
+  <si>
     <t>20141597</t>
   </si>
   <si>
@@ -664,12 +676,6 @@
     <t>YUPI LITTLE STARS 45</t>
   </si>
   <si>
-    <t>20141954</t>
-  </si>
-  <si>
-    <t>YUPI CRUNCY GUMMY 50</t>
-  </si>
-  <si>
     <t>20139394</t>
   </si>
   <si>
@@ -782,9 +788,6 @@
   </si>
   <si>
     <t>YUPI GUMMY KOR BBQ70</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
   </si>
   <si>
     <t>10000766</t>
@@ -1390,7 +1393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2894,10 +2897,10 @@
         <v>159</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2914,7 +2917,7 @@
         <v>159</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2934,7 +2937,7 @@
         <v>159</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2951,10 +2954,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2962,19 +2965,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2991,10 +2994,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3011,10 +3014,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3031,10 +3034,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3051,13 +3054,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3071,10 +3074,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>9</v>
@@ -3091,30 +3094,30 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3131,13 +3134,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3151,13 +3154,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3171,10 +3174,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3191,10 +3194,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3211,10 +3214,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3231,10 +3234,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3242,19 +3245,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3271,10 +3274,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3291,10 +3294,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3311,10 +3314,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3331,10 +3334,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3351,10 +3354,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3371,10 +3374,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3391,10 +3394,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3402,19 +3405,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3431,10 +3434,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3451,10 +3454,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3471,10 +3474,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3491,10 +3494,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3511,10 +3514,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3531,13 +3534,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3551,13 +3554,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3571,10 +3574,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3591,10 +3594,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3602,19 +3605,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3631,10 +3634,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3651,10 +3654,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3671,10 +3674,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3691,10 +3694,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3711,10 +3714,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3731,30 +3734,30 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3762,19 +3765,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3782,39 +3785,39 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>9</v>
@@ -3822,19 +3825,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>9</v>
@@ -3842,79 +3845,79 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3922,59 +3925,59 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>280</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3982,119 +3985,119 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>273</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4102,19 +4105,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4122,19 +4125,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4142,19 +4145,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4162,59 +4165,59 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4222,59 +4225,59 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>274</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4282,19 +4285,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4302,19 +4305,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4322,19 +4325,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4342,19 +4345,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4362,19 +4365,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4382,21 +4385,41 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F150" s="1" t="s">
+      <c r="B151" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="334">
   <si>
     <t/>
   </si>
@@ -352,7 +352,7 @@
     <t>20133639</t>
   </si>
   <si>
-    <t>DW DARK.CHO ALMND 56</t>
+    <t>DW DARK.CHO ALMND 40</t>
   </si>
   <si>
     <t>20089666</t>
@@ -625,6 +625,12 @@
     <t>YUPI KISS STRAW 110G</t>
   </si>
   <si>
+    <t>20142221</t>
+  </si>
+  <si>
+    <t>YUPI CND GMY FANGS90</t>
+  </si>
+  <si>
     <t>20140015</t>
   </si>
   <si>
@@ -644,6 +650,12 @@
   </si>
   <si>
     <t>FRUZZ GUMMY ASORTD36</t>
+  </si>
+  <si>
+    <t>20142223</t>
+  </si>
+  <si>
+    <t>BONCHA CND GUMMY 60G</t>
   </si>
   <si>
     <t>20138897</t>
@@ -1393,7 +1405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3254,10 +3266,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3265,19 +3277,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3294,10 +3306,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3314,10 +3326,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3334,10 +3346,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3354,10 +3366,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3374,10 +3386,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3394,10 +3406,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3414,10 +3426,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3425,19 +3437,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3445,19 +3457,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3474,10 +3486,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3494,10 +3506,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3514,10 +3526,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3534,10 +3546,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3554,13 +3566,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3574,10 +3586,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3594,13 +3606,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3614,10 +3626,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3625,19 +3637,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3645,19 +3657,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3674,10 +3686,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3694,10 +3706,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3714,10 +3726,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3734,10 +3746,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3754,10 +3766,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3774,10 +3786,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3785,19 +3797,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3805,22 +3817,22 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3834,13 +3846,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3854,10 +3866,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>9</v>
@@ -3874,13 +3886,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3894,30 +3906,30 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>274</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3925,22 +3937,22 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3954,30 +3966,30 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>281</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3985,22 +3997,22 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4014,53 +4026,53 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>159</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>274</v>
+        <v>33</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4074,13 +4086,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>281</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4094,13 +4106,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>278</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4114,13 +4126,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>5</v>
+        <v>285</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4134,10 +4146,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4154,10 +4166,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4174,10 +4186,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4185,39 +4197,39 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4234,13 +4246,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4254,13 +4266,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>274</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4274,10 +4286,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4294,13 +4306,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>278</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4314,10 +4326,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4334,10 +4346,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4354,10 +4366,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4374,10 +4386,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4394,10 +4406,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4414,12 +4426,52 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E151" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F151" s="1" t="s">
+      <c r="F153" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="324">
   <si>
     <t/>
   </si>
@@ -151,282 +151,264 @@
     <t>9</t>
   </si>
   <si>
-    <t>20083719</t>
-  </si>
-  <si>
-    <t>NANO MILKY COK 12G</t>
+    <t>20033392</t>
+  </si>
+  <si>
+    <t>DELFI CHACHA MINIS25</t>
+  </si>
+  <si>
+    <t>20077110</t>
+  </si>
+  <si>
+    <t>CHACHA MINIS HATS 25</t>
+  </si>
+  <si>
+    <t>20122057</t>
+  </si>
+  <si>
+    <t>CHACHA MINIS CAR12.5</t>
+  </si>
+  <si>
+    <t>20140016</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHO PEANUT 37G</t>
+  </si>
+  <si>
+    <t>20140013</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHOC CRSPY 30G</t>
+  </si>
+  <si>
+    <t>20129814</t>
+  </si>
+  <si>
+    <t>MLKITA CNDY BTES 24G</t>
+  </si>
+  <si>
+    <t>20140908</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD STRW 85G</t>
+  </si>
+  <si>
+    <t>20140907</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD MILK 85G</t>
+  </si>
+  <si>
+    <t>20045175</t>
+  </si>
+  <si>
+    <t>CHA CHA MILK CHO 20G</t>
+  </si>
+  <si>
+    <t>20045176</t>
+  </si>
+  <si>
+    <t>CHA CHA PNUT CHO 20G</t>
+  </si>
+  <si>
+    <t>20063093</t>
+  </si>
+  <si>
+    <t>DELFI MALTITOS 26</t>
+  </si>
+  <si>
+    <t>10000418</t>
+  </si>
+  <si>
+    <t>DELFI CHIC CHOC 36G</t>
+  </si>
+  <si>
+    <t>20024539</t>
+  </si>
+  <si>
+    <t>S/Q BITES ALMOND 30G</t>
+  </si>
+  <si>
+    <t>20128815</t>
+  </si>
+  <si>
+    <t>IDM GUMMY CHO MF 40G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140906</t>
+  </si>
+  <si>
+    <t>MILKITA BAR CHOC 15G</t>
+  </si>
+  <si>
+    <t>20140412</t>
+  </si>
+  <si>
+    <t>MILKITA MILKY BAR 15</t>
+  </si>
+  <si>
+    <t>20113490</t>
+  </si>
+  <si>
+    <t>BENG-BENG ALMOND 35G</t>
+  </si>
+  <si>
+    <t>20044008</t>
+  </si>
+  <si>
+    <t>BENG-BENG MAXX 32G</t>
+  </si>
+  <si>
+    <t>20117108</t>
+  </si>
+  <si>
+    <t>BENG-BENG PCK 3X20G</t>
+  </si>
+  <si>
+    <t>20112348</t>
+  </si>
+  <si>
+    <t>IDM BLUEBRY D.CHO 45</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20085730</t>
+  </si>
+  <si>
+    <t>IDM CASH MILK CHO 40</t>
+  </si>
+  <si>
+    <t>20093638</t>
+  </si>
+  <si>
+    <t>IDM BISC MILK CHO 40</t>
+  </si>
+  <si>
+    <t>20046198</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCOLAT 51</t>
+  </si>
+  <si>
+    <t>20011878</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCO 35G</t>
+  </si>
+  <si>
+    <t>10008315</t>
+  </si>
+  <si>
+    <t>KINDER BUENO CHO 43G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20139949</t>
+  </si>
+  <si>
+    <t>LMNILO CRNCHY CHO 18</t>
+  </si>
+  <si>
+    <t>20134029</t>
+  </si>
+  <si>
+    <t>DELFI TRSURE MLK2X30</t>
+  </si>
+  <si>
+    <t>20130547</t>
+  </si>
+  <si>
+    <t>DELFI CHOCO DM 2X25G</t>
+  </si>
+  <si>
+    <t>10000757</t>
+  </si>
+  <si>
+    <t>L'AGIE FULL MILK 60G</t>
+  </si>
+  <si>
+    <t>20120946</t>
+  </si>
+  <si>
+    <t>KINDER JOY DC COMICS</t>
+  </si>
+  <si>
+    <t>20133639</t>
+  </si>
+  <si>
+    <t>DW DARK.CHO ALMND 40</t>
+  </si>
+  <si>
+    <t>20089666</t>
+  </si>
+  <si>
+    <t>CADBURY CSHW NUT 85G</t>
+  </si>
+  <si>
+    <t>20062877</t>
+  </si>
+  <si>
+    <t>CADBURY BLCK.FOR 57G</t>
+  </si>
+  <si>
+    <t>20054753</t>
+  </si>
+  <si>
+    <t>CADBURY FRUIT&amp;NUT 52</t>
+  </si>
+  <si>
+    <t>20120257</t>
+  </si>
+  <si>
+    <t>CADBURY HAZELNUT 52G</t>
+  </si>
+  <si>
+    <t>20140883</t>
+  </si>
+  <si>
+    <t>CADBURY BUBBLY 46G</t>
+  </si>
+  <si>
+    <t>20008798</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY CASHEW 82</t>
+  </si>
+  <si>
+    <t>10036987</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHEW 52G</t>
+  </si>
+  <si>
+    <t>20092545</t>
+  </si>
+  <si>
+    <t>SLVR QUEEN MATCHA 52</t>
+  </si>
+  <si>
+    <t>20092546</t>
+  </si>
+  <si>
+    <t>SLVR QUEEN MATCHA 22</t>
+  </si>
+  <si>
+    <t>20140185</t>
+  </si>
+  <si>
+    <t>SQ CHUNKY MINIS 10X8</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20033392</t>
-  </si>
-  <si>
-    <t>DELFI CHACHA MINIS25</t>
-  </si>
-  <si>
-    <t>20077110</t>
-  </si>
-  <si>
-    <t>CHACHA MINIS HATS 25</t>
-  </si>
-  <si>
-    <t>20122057</t>
-  </si>
-  <si>
-    <t>CHACHA MINIS CAR12.5</t>
-  </si>
-  <si>
-    <t>20140016</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHO PEANUT 37G</t>
-  </si>
-  <si>
-    <t>20140013</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHOC CRSPY 30G</t>
-  </si>
-  <si>
-    <t>20129814</t>
-  </si>
-  <si>
-    <t>MLKITA CNDY BTES 24G</t>
-  </si>
-  <si>
-    <t>20140908</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD STRW 85G</t>
-  </si>
-  <si>
-    <t>20140907</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD MILK 85G</t>
-  </si>
-  <si>
-    <t>20045175</t>
-  </si>
-  <si>
-    <t>CHA CHA MILK CHO 20G</t>
-  </si>
-  <si>
-    <t>20045176</t>
-  </si>
-  <si>
-    <t>CHA CHA PNUT CHO 20G</t>
-  </si>
-  <si>
-    <t>20063093</t>
-  </si>
-  <si>
-    <t>DELFI MALTITOS 26</t>
-  </si>
-  <si>
-    <t>10000418</t>
-  </si>
-  <si>
-    <t>DELFI CHIC CHOC 36G</t>
-  </si>
-  <si>
-    <t>20024539</t>
-  </si>
-  <si>
-    <t>S/Q BITES ALMOND 30G</t>
-  </si>
-  <si>
-    <t>20128815</t>
-  </si>
-  <si>
-    <t>IDM GUMMY CHO MF 40G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140906</t>
-  </si>
-  <si>
-    <t>MILKITA BAR CHOC 15G</t>
-  </si>
-  <si>
-    <t>20140412</t>
-  </si>
-  <si>
-    <t>MILKITA MILKY BAR 15</t>
-  </si>
-  <si>
-    <t>20113490</t>
-  </si>
-  <si>
-    <t>BENG-BENG ALMOND 35G</t>
-  </si>
-  <si>
-    <t>20044008</t>
-  </si>
-  <si>
-    <t>BENG-BENG MAXX 32G</t>
-  </si>
-  <si>
-    <t>20117108</t>
-  </si>
-  <si>
-    <t>BENG-BENG PCK 3X20G</t>
-  </si>
-  <si>
-    <t>20112348</t>
-  </si>
-  <si>
-    <t>IDM BLUEBRY D.CHO 45</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20085730</t>
-  </si>
-  <si>
-    <t>IDM CASH MILK CHO 40</t>
-  </si>
-  <si>
-    <t>20093638</t>
-  </si>
-  <si>
-    <t>IDM BISC MILK CHO 40</t>
-  </si>
-  <si>
-    <t>20046198</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCOLAT 51</t>
-  </si>
-  <si>
-    <t>20011878</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCO 35G</t>
-  </si>
-  <si>
-    <t>10008315</t>
-  </si>
-  <si>
-    <t>KINDER BUENO CHO 43G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20139949</t>
-  </si>
-  <si>
-    <t>LMNILO CRNCHY CHO 18</t>
-  </si>
-  <si>
-    <t>20134029</t>
-  </si>
-  <si>
-    <t>DELFI TRSURE MLK2X30</t>
-  </si>
-  <si>
-    <t>20130547</t>
-  </si>
-  <si>
-    <t>DELFI CHOCO DM 2X25G</t>
-  </si>
-  <si>
-    <t>10000757</t>
-  </si>
-  <si>
-    <t>L'AGIE FULL MILK 60G</t>
-  </si>
-  <si>
-    <t>20120946</t>
-  </si>
-  <si>
-    <t>KINDER JOY DC COMICS</t>
-  </si>
-  <si>
-    <t>20133639</t>
-  </si>
-  <si>
-    <t>DW DARK.CHO ALMND 40</t>
-  </si>
-  <si>
-    <t>20089666</t>
-  </si>
-  <si>
-    <t>CADBURY CSHW NUT 85G</t>
-  </si>
-  <si>
-    <t>20062877</t>
-  </si>
-  <si>
-    <t>CADBURY BLCK.FOR 57G</t>
-  </si>
-  <si>
-    <t>20054753</t>
-  </si>
-  <si>
-    <t>CADBURY FRUIT&amp;NUT 52</t>
-  </si>
-  <si>
-    <t>20120257</t>
-  </si>
-  <si>
-    <t>CADBURY HAZELNUT 52G</t>
-  </si>
-  <si>
-    <t>20140883</t>
-  </si>
-  <si>
-    <t>CADBURY BUBBLY 46G</t>
-  </si>
-  <si>
-    <t>20141062</t>
-  </si>
-  <si>
-    <t>SQ CHUNKY CUPID 3X26</t>
-  </si>
-  <si>
-    <t>20141063</t>
-  </si>
-  <si>
-    <t>SQ CSHW BTRFLY 3X22G</t>
-  </si>
-  <si>
-    <t>20008798</t>
-  </si>
-  <si>
-    <t>S/Q CHUNKY CASHEW 82</t>
-  </si>
-  <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
-  </si>
-  <si>
-    <t>20092545</t>
-  </si>
-  <si>
-    <t>SLVR QUEEN MATCHA 52</t>
-  </si>
-  <si>
-    <t>20092546</t>
-  </si>
-  <si>
-    <t>SLVR QUEEN MATCHA 22</t>
-  </si>
-  <si>
-    <t>20140185</t>
-  </si>
-  <si>
-    <t>SQ CHUNKY MINIS 10X8</t>
-  </si>
-  <si>
     <t>TG,(E-1B)</t>
   </si>
   <si>
@@ -587,18 +569,6 @@
   </si>
   <si>
     <t>13</t>
-  </si>
-  <si>
-    <t>20082651</t>
-  </si>
-  <si>
-    <t>BIG BB FLFLY TTFR 11</t>
-  </si>
-  <si>
-    <t>20113106</t>
-  </si>
-  <si>
-    <t>YUPI SWT ARTIFACT 77</t>
   </si>
   <si>
     <t>10013885</t>
@@ -1405,7 +1375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1766,21 +1736,21 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1789,7 +1759,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1797,10 +1767,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1809,7 +1779,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1817,10 +1787,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1829,7 +1799,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1837,10 +1807,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1849,7 +1819,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1857,10 +1827,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1869,7 +1839,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1877,10 +1847,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1889,7 +1859,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1897,10 +1867,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1909,7 +1879,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1917,19 +1887,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1937,10 +1907,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1949,7 +1919,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1957,10 +1927,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1969,7 +1939,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1977,10 +1947,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1989,7 +1959,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1997,10 +1967,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2009,7 +1979,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2017,22 +1987,22 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2049,18 +2019,18 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2069,7 +2039,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2077,10 +2047,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2089,7 +2059,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2097,10 +2067,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2109,7 +2079,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2117,10 +2087,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2129,7 +2099,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2137,22 +2107,22 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2169,18 +2139,18 @@
         <v>21</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2189,18 +2159,18 @@
         <v>21</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2209,18 +2179,18 @@
         <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2229,7 +2199,7 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2237,10 +2207,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2249,10 +2219,10 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2269,27 +2239,27 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2297,10 +2267,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2309,7 +2279,7 @@
         <v>24</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2317,10 +2287,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2329,18 +2299,18 @@
         <v>24</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2349,27 +2319,27 @@
         <v>24</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2377,10 +2347,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2389,7 +2359,7 @@
         <v>42</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2397,10 +2367,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2409,7 +2379,7 @@
         <v>42</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2417,10 +2387,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2429,7 +2399,7 @@
         <v>42</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2437,10 +2407,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2449,7 +2419,7 @@
         <v>42</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2457,10 +2427,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2469,7 +2439,7 @@
         <v>42</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2477,19 +2447,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2497,10 +2467,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2509,7 +2479,7 @@
         <v>45</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2517,10 +2487,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2529,7 +2499,7 @@
         <v>45</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2537,10 +2507,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2549,7 +2519,7 @@
         <v>45</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2557,39 +2527,39 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2597,19 +2567,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2617,22 +2587,22 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>138</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2646,13 +2616,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2666,13 +2636,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2686,13 +2656,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2706,13 +2676,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2726,13 +2696,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2746,13 +2716,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2766,30 +2736,30 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2797,39 +2767,39 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2846,13 +2816,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2866,10 +2836,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2886,10 +2856,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2906,13 +2876,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2926,10 +2896,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2937,19 +2907,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2957,19 +2927,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2977,19 +2947,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3006,10 +2976,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3026,13 +2996,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3046,13 +3016,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3066,10 +3036,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3077,59 +3047,59 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="E84" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3146,10 +3116,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3166,13 +3136,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3186,10 +3156,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3197,19 +3167,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3217,19 +3187,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3237,19 +3207,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3257,19 +3227,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3277,19 +3247,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3306,10 +3276,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3326,10 +3296,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3346,10 +3316,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3366,10 +3336,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3377,19 +3347,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3397,19 +3367,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3417,19 +3387,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3437,19 +3407,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3457,19 +3427,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3486,10 +3456,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3506,13 +3476,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3526,10 +3496,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3546,10 +3516,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3566,10 +3536,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3577,19 +3547,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3597,39 +3567,39 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3637,19 +3607,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3657,19 +3627,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3686,10 +3656,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3706,10 +3676,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3726,10 +3696,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3737,19 +3707,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3757,79 +3727,79 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3846,90 +3816,90 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>9</v>
+        <v>275</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3937,119 +3907,119 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>278</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>275</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4057,22 +4027,22 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4086,13 +4056,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4106,13 +4076,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>278</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4126,50 +4096,50 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>285</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4177,19 +4147,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4197,39 +4167,39 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>268</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4246,13 +4216,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4266,10 +4236,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4286,10 +4256,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4306,13 +4276,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>278</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4326,10 +4296,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4346,10 +4316,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4366,112 +4336,12 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F153" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="326">
   <si>
     <t/>
   </si>
@@ -100,12 +100,189 @@
     <t>CHOKI CHOKI 6X4G</t>
   </si>
   <si>
+    <t>20128815</t>
+  </si>
+  <si>
+    <t>IDM GUMMY CHO MF 40G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
     <t>10000322</t>
   </si>
   <si>
     <t>CHOKI CHOKI CHO 4X9G</t>
   </si>
   <si>
+    <t>20141002</t>
+  </si>
+  <si>
+    <t>WONHAE MTCHA BRY 30G</t>
+  </si>
+  <si>
+    <t>20139890</t>
+  </si>
+  <si>
+    <t>WNHAE STRW CHEESCAKE</t>
+  </si>
+  <si>
+    <t>20139889</t>
+  </si>
+  <si>
+    <t>WNHAE PISTACHIO CHOC</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20135198</t>
+  </si>
+  <si>
+    <t>WONHAE YOG.GUM ORI48</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20135661</t>
+  </si>
+  <si>
+    <t>WNHAE GMMY MXD.FRT32</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20033392</t>
+  </si>
+  <si>
+    <t>DELFI CHACHA MINIS25</t>
+  </si>
+  <si>
+    <t>20077110</t>
+  </si>
+  <si>
+    <t>CHACHA MINIS HATS 25</t>
+  </si>
+  <si>
+    <t>20122057</t>
+  </si>
+  <si>
+    <t>CHACHA MINIS CAR12.5</t>
+  </si>
+  <si>
+    <t>20140016</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHO PEANUT 37G</t>
+  </si>
+  <si>
+    <t>20140013</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHOC CRSPY 30G</t>
+  </si>
+  <si>
+    <t>20129814</t>
+  </si>
+  <si>
+    <t>MLKITA CNDY BTES 24G</t>
+  </si>
+  <si>
+    <t>20140908</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD STRW 85G</t>
+  </si>
+  <si>
+    <t>20140907</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD MILK 85G</t>
+  </si>
+  <si>
+    <t>20045175</t>
+  </si>
+  <si>
+    <t>CHA CHA MILK CHO 20G</t>
+  </si>
+  <si>
+    <t>20045176</t>
+  </si>
+  <si>
+    <t>CHA CHA PNUT CHO 20G</t>
+  </si>
+  <si>
+    <t>20063093</t>
+  </si>
+  <si>
+    <t>DELFI MALTITOS 26</t>
+  </si>
+  <si>
+    <t>10000418</t>
+  </si>
+  <si>
+    <t>DELFI CHIC CHOC 36G</t>
+  </si>
+  <si>
+    <t>20024539</t>
+  </si>
+  <si>
+    <t>S/Q BITES ALMOND 30G</t>
+  </si>
+  <si>
+    <t>20140906</t>
+  </si>
+  <si>
+    <t>MILKITA BAR CHOC 15G</t>
+  </si>
+  <si>
+    <t>20140412</t>
+  </si>
+  <si>
+    <t>MILKITA MILKY BAR 15</t>
+  </si>
+  <si>
+    <t>20113490</t>
+  </si>
+  <si>
+    <t>BENG-BENG ALMOND 35G</t>
+  </si>
+  <si>
+    <t>20044008</t>
+  </si>
+  <si>
+    <t>BENG-BENG MAXX 32G</t>
+  </si>
+  <si>
+    <t>20117108</t>
+  </si>
+  <si>
+    <t>BENG-BENG PCK 3X20G</t>
+  </si>
+  <si>
+    <t>20112348</t>
+  </si>
+  <si>
+    <t>IDM BLUEBRY D.CHO 45</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20085730</t>
+  </si>
+  <si>
+    <t>IDM CASH MILK CHO 40</t>
+  </si>
+  <si>
+    <t>20093638</t>
+  </si>
+  <si>
+    <t>IDM BISC MILK CHO 40</t>
+  </si>
+  <si>
     <t>20084899</t>
   </si>
   <si>
@@ -115,178 +292,10 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20141002</t>
-  </si>
-  <si>
-    <t>WONHAE MTCHA BRY 30G</t>
-  </si>
-  <si>
-    <t>20139890</t>
-  </si>
-  <si>
-    <t>WNHAE STRW CHEESCAKE</t>
-  </si>
-  <si>
-    <t>20139889</t>
-  </si>
-  <si>
-    <t>WNHAE PISTACHIO CHOC</t>
-  </si>
-  <si>
-    <t>20135198</t>
-  </si>
-  <si>
-    <t>WONHAE YOG.GUM ORI48</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20135661</t>
-  </si>
-  <si>
-    <t>WNHAE GMMY MXD.FRT32</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20033392</t>
-  </si>
-  <si>
-    <t>DELFI CHACHA MINIS25</t>
-  </si>
-  <si>
-    <t>20077110</t>
-  </si>
-  <si>
-    <t>CHACHA MINIS HATS 25</t>
-  </si>
-  <si>
-    <t>20122057</t>
-  </si>
-  <si>
-    <t>CHACHA MINIS CAR12.5</t>
-  </si>
-  <si>
-    <t>20140016</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHO PEANUT 37G</t>
-  </si>
-  <si>
-    <t>20140013</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHOC CRSPY 30G</t>
-  </si>
-  <si>
-    <t>20129814</t>
-  </si>
-  <si>
-    <t>MLKITA CNDY BTES 24G</t>
-  </si>
-  <si>
-    <t>20140908</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD STRW 85G</t>
-  </si>
-  <si>
-    <t>20140907</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD MILK 85G</t>
-  </si>
-  <si>
-    <t>20045175</t>
-  </si>
-  <si>
-    <t>CHA CHA MILK CHO 20G</t>
-  </si>
-  <si>
-    <t>20045176</t>
-  </si>
-  <si>
-    <t>CHA CHA PNUT CHO 20G</t>
-  </si>
-  <si>
-    <t>20063093</t>
-  </si>
-  <si>
-    <t>DELFI MALTITOS 26</t>
-  </si>
-  <si>
-    <t>10000418</t>
-  </si>
-  <si>
-    <t>DELFI CHIC CHOC 36G</t>
-  </si>
-  <si>
-    <t>20024539</t>
-  </si>
-  <si>
-    <t>S/Q BITES ALMOND 30G</t>
-  </si>
-  <si>
-    <t>20128815</t>
-  </si>
-  <si>
-    <t>IDM GUMMY CHO MF 40G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140906</t>
-  </si>
-  <si>
-    <t>MILKITA BAR CHOC 15G</t>
-  </si>
-  <si>
-    <t>20140412</t>
-  </si>
-  <si>
-    <t>MILKITA MILKY BAR 15</t>
-  </si>
-  <si>
-    <t>20113490</t>
-  </si>
-  <si>
-    <t>BENG-BENG ALMOND 35G</t>
-  </si>
-  <si>
-    <t>20044008</t>
-  </si>
-  <si>
-    <t>BENG-BENG MAXX 32G</t>
-  </si>
-  <si>
-    <t>20117108</t>
-  </si>
-  <si>
-    <t>BENG-BENG PCK 3X20G</t>
-  </si>
-  <si>
-    <t>20112348</t>
-  </si>
-  <si>
-    <t>IDM BLUEBRY D.CHO 45</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20085730</t>
-  </si>
-  <si>
-    <t>IDM CASH MILK CHO 40</t>
-  </si>
-  <si>
-    <t>20093638</t>
-  </si>
-  <si>
-    <t>IDM BISC MILK CHO 40</t>
+    <t>20065363</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCOLAT 70</t>
   </si>
   <si>
     <t>20046198</t>
@@ -301,6 +310,36 @@
     <t>SNICKERS CHOCO 35G</t>
   </si>
   <si>
+    <t>20139949</t>
+  </si>
+  <si>
+    <t>LMNILO CRNCHY CHO 18</t>
+  </si>
+  <si>
+    <t>20120946</t>
+  </si>
+  <si>
+    <t>KINDER JOY DC COMICS</t>
+  </si>
+  <si>
+    <t>20130547</t>
+  </si>
+  <si>
+    <t>DELFI CHOCO DM 2X25G</t>
+  </si>
+  <si>
+    <t>20134029</t>
+  </si>
+  <si>
+    <t>DELFI TRSURE MLK2X30</t>
+  </si>
+  <si>
+    <t>10000757</t>
+  </si>
+  <si>
+    <t>L'AGIE FULL MILK 60G</t>
+  </si>
+  <si>
     <t>10008315</t>
   </si>
   <si>
@@ -310,40 +349,28 @@
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20139949</t>
-  </si>
-  <si>
-    <t>LMNILO CRNCHY CHO 18</t>
-  </si>
-  <si>
-    <t>20134029</t>
-  </si>
-  <si>
-    <t>DELFI TRSURE MLK2X30</t>
-  </si>
-  <si>
-    <t>20130547</t>
-  </si>
-  <si>
-    <t>DELFI CHOCO DM 2X25G</t>
-  </si>
-  <si>
-    <t>10000757</t>
-  </si>
-  <si>
-    <t>L'AGIE FULL MILK 60G</t>
-  </si>
-  <si>
-    <t>20120946</t>
-  </si>
-  <si>
-    <t>KINDER JOY DC COMICS</t>
-  </si>
-  <si>
-    <t>20133639</t>
-  </si>
-  <si>
-    <t>DW DARK.CHO ALMND 40</t>
+    <t>20062877</t>
+  </si>
+  <si>
+    <t>CADBURY BLCK.FOR 57G</t>
+  </si>
+  <si>
+    <t>20054753</t>
+  </si>
+  <si>
+    <t>CADBURY FRUIT&amp;NUT 52</t>
+  </si>
+  <si>
+    <t>20120257</t>
+  </si>
+  <si>
+    <t>CADBURY HAZELNUT 52G</t>
+  </si>
+  <si>
+    <t>20140883</t>
+  </si>
+  <si>
+    <t>CADBURY BUBBLY 46G</t>
   </si>
   <si>
     <t>20089666</t>
@@ -352,28 +379,10 @@
     <t>CADBURY CSHW NUT 85G</t>
   </si>
   <si>
-    <t>20062877</t>
-  </si>
-  <si>
-    <t>CADBURY BLCK.FOR 57G</t>
-  </si>
-  <si>
-    <t>20054753</t>
-  </si>
-  <si>
-    <t>CADBURY FRUIT&amp;NUT 52</t>
-  </si>
-  <si>
-    <t>20120257</t>
-  </si>
-  <si>
-    <t>CADBURY HAZELNUT 52G</t>
-  </si>
-  <si>
-    <t>20140883</t>
-  </si>
-  <si>
-    <t>CADBURY BUBBLY 46G</t>
+    <t>20142508</t>
+  </si>
+  <si>
+    <t>DARK WONDER  BDD2X40</t>
   </si>
   <si>
     <t>20008798</t>
@@ -406,9 +415,6 @@
     <t>SQ CHUNKY MINIS 10X8</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>TG,(E-1B)</t>
   </si>
   <si>
@@ -571,6 +577,12 @@
     <t>13</t>
   </si>
   <si>
+    <t>20142221</t>
+  </si>
+  <si>
+    <t>YUPI CND GMY FANGS90</t>
+  </si>
+  <si>
     <t>10013885</t>
   </si>
   <si>
@@ -595,12 +607,6 @@
     <t>YUPI KISS STRAW 110G</t>
   </si>
   <si>
-    <t>20142221</t>
-  </si>
-  <si>
-    <t>YUPI CND GMY FANGS90</t>
-  </si>
-  <si>
     <t>20140015</t>
   </si>
   <si>
@@ -787,6 +793,12 @@
     <t>SUGUS STICK BLCRNT30</t>
   </si>
   <si>
+    <t>20138041</t>
+  </si>
+  <si>
+    <t>FROZZ MANGO BINGSO14</t>
+  </si>
+  <si>
     <t>20014081</t>
   </si>
   <si>
@@ -805,12 +817,6 @@
     <t>FROZZ CHERRY MINT 15</t>
   </si>
   <si>
-    <t>20138041</t>
-  </si>
-  <si>
-    <t>FROZZ MANGO BINGSO14</t>
-  </si>
-  <si>
     <t>20067474</t>
   </si>
   <si>
@@ -853,31 +859,31 @@
     <t>MILTON PSTLS LMN16.5</t>
   </si>
   <si>
+    <t>10011038</t>
+  </si>
+  <si>
+    <t>WOODS PEP.EXT/STRG15</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20109048</t>
+  </si>
+  <si>
+    <t>HEXOS MINT 8'S</t>
+  </si>
+  <si>
+    <t>10033024</t>
+  </si>
+  <si>
+    <t>S/M CANDY TLK.AGN 5S</t>
+  </si>
+  <si>
     <t>20099973</t>
   </si>
   <si>
     <t>HMLYA SL CNDY LMN 15</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20109048</t>
-  </si>
-  <si>
-    <t>HEXOS MINT 8'S</t>
-  </si>
-  <si>
-    <t>10011038</t>
-  </si>
-  <si>
-    <t>WOODS PEP.EXT/STRG15</t>
-  </si>
-  <si>
-    <t>10033024</t>
-  </si>
-  <si>
-    <t>S/M CANDY TLK.AGN 5S</t>
   </si>
   <si>
     <t>20110265</t>
@@ -1375,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1579,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -1599,18 +1605,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1619,10 +1625,10 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1639,7 +1645,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1659,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1679,7 +1685,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1687,10 +1693,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1699,7 +1705,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1707,10 +1713,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1719,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1727,10 +1733,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1747,10 +1753,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1767,10 +1773,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1787,10 +1793,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1799,7 +1805,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1807,10 +1813,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1819,7 +1825,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1827,10 +1833,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1839,7 +1845,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1847,10 +1853,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1859,7 +1865,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1867,10 +1873,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1879,7 +1885,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1887,10 +1893,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1907,10 +1913,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1919,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1927,10 +1933,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1947,10 +1953,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1967,10 +1973,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1987,10 +1993,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2002,7 +2008,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2039,7 +2045,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2059,7 +2065,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2079,7 +2085,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2096,21 +2102,21 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2119,10 +2125,10 @@
         <v>21</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,10 +2145,10 @@
         <v>21</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2159,18 +2165,18 @@
         <v>21</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2179,7 +2185,7 @@
         <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2187,10 +2193,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2199,7 +2205,7 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2207,10 +2213,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2219,10 +2225,10 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2239,7 +2245,7 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2259,7 +2265,7 @@
         <v>24</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2302,7 +2308,7 @@
         <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2322,7 +2328,7 @@
         <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2336,30 +2342,30 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2367,19 +2373,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2387,19 +2393,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2407,19 +2413,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2427,19 +2433,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2447,19 +2453,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2467,19 +2473,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2487,19 +2493,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2507,19 +2513,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2527,42 +2533,42 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2576,10 +2582,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2596,10 +2602,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2616,13 +2622,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2636,13 +2642,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2656,13 +2662,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2676,13 +2682,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2696,13 +2702,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2716,13 +2722,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2736,30 +2742,30 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2776,10 +2782,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2796,10 +2802,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2816,13 +2822,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2836,13 +2842,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2856,10 +2862,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2876,10 +2882,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2896,10 +2902,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2907,19 +2913,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2936,10 +2942,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2956,10 +2962,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2976,10 +2982,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2996,13 +3002,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3016,10 +3022,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>9</v>
@@ -3036,30 +3042,30 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="E84" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3076,10 +3082,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3096,10 +3102,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3116,10 +3122,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3136,10 +3142,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3156,10 +3162,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3167,19 +3173,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3196,10 +3202,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3216,10 +3222,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3236,10 +3242,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3256,10 +3262,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3276,10 +3282,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3296,10 +3302,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3316,10 +3322,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3336,10 +3342,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3347,19 +3353,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3376,10 +3382,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3396,10 +3402,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3416,10 +3422,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3436,10 +3442,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3456,10 +3462,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3476,13 +3482,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3496,13 +3502,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3516,10 +3522,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3536,10 +3542,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3547,19 +3553,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3576,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3596,10 +3602,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3616,10 +3622,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3636,10 +3642,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3656,10 +3662,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3676,10 +3682,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3696,10 +3702,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3707,19 +3713,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3736,13 +3742,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3756,13 +3762,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3776,7 +3782,7 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>18</v>
@@ -3796,13 +3802,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3816,33 +3822,33 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>268</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3856,10 +3862,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3876,33 +3882,33 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>275</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3916,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3936,33 +3942,33 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>9</v>
+        <v>270</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3976,13 +3982,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>268</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3996,13 +4002,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4016,13 +4022,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4036,7 +4042,7 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>21</v>
@@ -4056,7 +4062,7 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>24</v>
@@ -4076,10 +4082,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4096,10 +4102,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4107,22 +4113,22 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4136,13 +4142,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4156,10 +4162,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4176,13 +4182,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>268</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4196,13 +4202,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>270</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4216,10 +4222,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4236,10 +4242,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4256,10 +4262,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4276,10 +4282,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4296,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4316,10 +4322,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4336,12 +4342,32 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="F148" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F149" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="328">
   <si>
     <t/>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>KINDER JOY DC COMICS</t>
+  </si>
+  <si>
+    <t>20142332</t>
+  </si>
+  <si>
+    <t>LARIST CHOCO EGG 20G</t>
   </si>
   <si>
     <t>20130547</t>
@@ -1381,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2285,7 +2291,7 @@
         <v>24</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2305,7 +2311,7 @@
         <v>24</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2325,10 +2331,10 @@
         <v>24</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2345,30 +2351,30 @@
         <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2385,7 +2391,7 @@
         <v>40</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2405,7 +2411,7 @@
         <v>40</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2425,7 +2431,7 @@
         <v>40</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2445,7 +2451,7 @@
         <v>40</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2462,10 +2468,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2485,7 +2491,7 @@
         <v>43</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2505,7 +2511,7 @@
         <v>43</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2525,7 +2531,7 @@
         <v>43</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2545,7 +2551,7 @@
         <v>43</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2562,21 +2568,21 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>134</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2585,10 +2591,10 @@
         <v>46</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2605,7 +2611,7 @@
         <v>46</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2625,7 +2631,7 @@
         <v>46</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2645,10 +2651,10 @@
         <v>46</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2665,7 +2671,7 @@
         <v>46</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>31</v>
@@ -2685,7 +2691,7 @@
         <v>46</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>31</v>
@@ -2705,7 +2711,7 @@
         <v>46</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>31</v>
@@ -2725,10 +2731,10 @@
         <v>46</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2745,10 +2751,10 @@
         <v>46</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2765,27 +2771,27 @@
         <v>46</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2802,10 +2808,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2822,10 +2828,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2842,13 +2848,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2862,13 +2868,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2882,10 +2888,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2902,10 +2908,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2922,10 +2928,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2933,19 +2939,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2962,10 +2968,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2982,10 +2988,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3002,10 +3008,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3022,13 +3028,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3042,10 +3048,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>9</v>
@@ -3062,30 +3068,30 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3102,10 +3108,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3122,10 +3128,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3142,10 +3148,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3162,10 +3168,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3182,10 +3188,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3193,19 +3199,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3222,10 +3228,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3242,10 +3248,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3262,10 +3268,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3282,10 +3288,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3302,10 +3308,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3322,10 +3328,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3342,10 +3348,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3362,10 +3368,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3373,19 +3379,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3402,10 +3408,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3422,10 +3428,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3442,10 +3448,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3462,10 +3468,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3482,10 +3488,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3502,13 +3508,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3522,13 +3528,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3542,10 +3548,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3562,10 +3568,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3573,19 +3579,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3602,10 +3608,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3622,10 +3628,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3642,10 +3648,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3662,10 +3668,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3682,10 +3688,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3702,10 +3708,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3722,10 +3728,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3733,19 +3739,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3762,10 +3768,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3782,13 +3788,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3802,10 +3808,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>9</v>
@@ -3822,10 +3828,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>9</v>
@@ -3842,33 +3848,33 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>270</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3882,10 +3888,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3902,33 +3908,33 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3942,10 +3948,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3962,33 +3968,33 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>270</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>9</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4002,13 +4008,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>277</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4022,13 +4028,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>92</v>
+        <v>279</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4042,13 +4048,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4062,10 +4068,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4082,10 +4088,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4102,10 +4108,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4122,10 +4128,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4133,22 +4139,22 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4162,13 +4168,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,10 +4188,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4202,13 +4208,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>270</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4222,13 +4228,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>272</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4242,10 +4248,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4262,10 +4268,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4282,10 +4288,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4302,10 +4308,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4322,10 +4328,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4342,10 +4348,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4362,12 +4368,32 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="F149" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F150" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="331">
   <si>
     <t/>
   </si>
@@ -208,6 +208,12 @@
     <t>CHA CHA MILK CHO 20G</t>
   </si>
   <si>
+    <t>20142588</t>
+  </si>
+  <si>
+    <t>CHA CHA PNUT CHO2X35</t>
+  </si>
+  <si>
     <t>20045176</t>
   </si>
   <si>
@@ -244,6 +250,12 @@
     <t>MILKITA MILKY BAR 15</t>
   </si>
   <si>
+    <t>20142589</t>
+  </si>
+  <si>
+    <t>DELFI NOCKER BDD2X35</t>
+  </si>
+  <si>
     <t>20113490</t>
   </si>
   <si>
@@ -419,9 +431,6 @@
   </si>
   <si>
     <t>SQ CHUNKY MINIS 10X8</t>
-  </si>
-  <si>
-    <t>TG,(E-1B)</t>
   </si>
   <si>
     <t>20130159</t>
@@ -1387,7 +1396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1931,7 +1940,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1951,7 +1960,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1971,7 +1980,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1991,7 +2000,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2008,10 +2017,10 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2031,7 +2040,7 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2051,7 +2060,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2071,7 +2080,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2091,7 +2100,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2108,41 +2117,41 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F37" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2151,10 +2160,10 @@
         <v>21</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2171,18 +2180,18 @@
         <v>21</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2191,18 +2200,18 @@
         <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2211,10 +2220,10 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2231,7 +2240,7 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2251,7 +2260,7 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2268,10 +2277,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2288,10 +2297,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2311,7 +2320,7 @@
         <v>24</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2331,7 +2340,7 @@
         <v>24</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2351,10 +2360,10 @@
         <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2371,50 +2380,50 @@
         <v>24</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>113</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2431,7 +2440,7 @@
         <v>40</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2451,7 +2460,7 @@
         <v>40</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2471,7 +2480,7 @@
         <v>40</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2488,10 +2497,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2508,10 +2517,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2531,7 +2540,7 @@
         <v>43</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2551,7 +2560,7 @@
         <v>43</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2571,7 +2580,7 @@
         <v>43</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2588,30 +2597,30 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>136</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2619,10 +2628,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2631,7 +2640,7 @@
         <v>46</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2639,10 +2648,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2651,7 +2660,7 @@
         <v>46</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2659,10 +2668,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2671,18 +2680,18 @@
         <v>46</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2691,18 +2700,18 @@
         <v>46</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2711,7 +2720,7 @@
         <v>46</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>31</v>
@@ -2719,10 +2728,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2731,7 +2740,7 @@
         <v>46</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>31</v>
@@ -2739,10 +2748,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2751,18 +2760,18 @@
         <v>46</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2771,18 +2780,18 @@
         <v>46</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2791,7 +2800,7 @@
         <v>46</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2799,39 +2808,39 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>46</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2839,19 +2848,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2859,39 +2868,39 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2899,39 +2908,39 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2939,19 +2948,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2959,19 +2968,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2979,19 +2988,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2999,19 +3008,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3019,19 +3028,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3039,99 +3048,99 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3139,19 +3148,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3159,19 +3168,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3179,19 +3188,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3199,19 +3208,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3219,19 +3228,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3239,19 +3248,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3259,19 +3268,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3279,19 +3288,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3299,19 +3308,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3319,19 +3328,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3339,19 +3348,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3359,19 +3368,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3379,19 +3388,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3399,19 +3408,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3419,19 +3428,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3439,19 +3448,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3459,19 +3468,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3479,19 +3488,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3499,19 +3508,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3519,39 +3528,39 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3559,39 +3568,39 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3599,19 +3608,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3619,19 +3628,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3639,19 +3648,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3659,19 +3668,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3679,19 +3688,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3699,19 +3708,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3719,19 +3728,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3739,19 +3748,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3759,19 +3768,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3779,19 +3788,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3799,59 +3808,59 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>9</v>
@@ -3859,99 +3868,99 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>272</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>279</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3959,159 +3968,159 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>272</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>282</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4119,19 +4128,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4139,19 +4148,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4159,39 +4168,39 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4199,59 +4208,59 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>272</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4259,39 +4268,39 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>275</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4299,19 +4308,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4319,19 +4328,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4339,19 +4348,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4359,19 +4368,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4379,21 +4388,61 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F150" s="1" t="s">
+      <c r="B151" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -949,13 +949,13 @@
     <t>20016240</t>
   </si>
   <si>
-    <t>FOX'S CRYST.BERIES90</t>
+    <t>FOX'S CRYST.BERIES80</t>
   </si>
   <si>
     <t>10000763</t>
   </si>
   <si>
-    <t>FOX'S CANDY FRUIT 90</t>
+    <t>FOX'S CANDY FRUIT 80</t>
   </si>
   <si>
     <t>10028390</t>
@@ -979,7 +979,7 @@
     <t>20094668</t>
   </si>
   <si>
-    <t>HPYDNT COOL MINT 28G</t>
+    <t>HPYDNT C/G COOL MINT</t>
   </si>
   <si>
     <t>20138379</t>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="330">
   <si>
     <t/>
   </si>
@@ -385,12 +385,6 @@
     <t>CADBURY HAZELNUT 52G</t>
   </si>
   <si>
-    <t>20140883</t>
-  </si>
-  <si>
-    <t>CADBURY BUBBLY 46G</t>
-  </si>
-  <si>
     <t>20089666</t>
   </si>
   <si>
@@ -412,7 +406,7 @@
     <t>10036987</t>
   </si>
   <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>S/Q CHOCO CASHW 52 G</t>
   </si>
   <si>
     <t>20092545</t>
@@ -505,7 +499,7 @@
     <t>10037013</t>
   </si>
   <si>
-    <t>RELAXA BARLEY MNT108</t>
+    <t>RELAXA BARLEY MNT 81</t>
   </si>
   <si>
     <t>20043035</t>
@@ -808,12 +802,6 @@
     <t>SUGUS STICK BLCRNT30</t>
   </si>
   <si>
-    <t>20138041</t>
-  </si>
-  <si>
-    <t>FROZZ MANGO BINGSO14</t>
-  </si>
-  <si>
     <t>20014081</t>
   </si>
   <si>
@@ -874,6 +862,15 @@
     <t>MILTON PSTLS LMN16.5</t>
   </si>
   <si>
+    <t>20129719</t>
+  </si>
+  <si>
+    <t>FROZZ ANGGR MINT 14G</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
     <t>10011038</t>
   </si>
   <si>
@@ -973,7 +970,7 @@
     <t>20018396</t>
   </si>
   <si>
-    <t>H/WHITE GUM BTL 44'S</t>
+    <t>H/WHITE GUM BTL 40'S</t>
   </si>
   <si>
     <t>20094668</t>
@@ -1396,14 +1393,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2500,7 +2497,7 @@
         <v>40</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2517,10 +2514,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2540,7 +2537,7 @@
         <v>43</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2560,7 +2557,7 @@
         <v>43</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2580,7 +2577,7 @@
         <v>43</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2600,7 +2597,7 @@
         <v>43</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2617,10 +2614,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2640,7 +2637,7 @@
         <v>46</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2660,7 +2657,7 @@
         <v>46</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2680,7 +2677,7 @@
         <v>46</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2700,10 +2697,10 @@
         <v>46</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2720,7 +2717,7 @@
         <v>46</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>31</v>
@@ -2740,7 +2737,7 @@
         <v>46</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>31</v>
@@ -2760,7 +2757,7 @@
         <v>46</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>31</v>
@@ -2780,10 +2777,10 @@
         <v>46</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2800,10 +2797,10 @@
         <v>46</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2820,27 +2817,27 @@
         <v>46</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>46</v>
+        <v>158</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2857,10 +2854,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2877,10 +2874,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2897,13 +2894,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2917,13 +2914,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2937,10 +2934,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2957,10 +2954,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2977,10 +2974,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2988,19 +2985,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3017,10 +3014,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3037,10 +3034,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3057,10 +3054,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3077,13 +3074,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3097,10 +3094,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>9</v>
@@ -3117,30 +3114,30 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3157,10 +3154,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3177,10 +3174,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3197,10 +3194,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3217,10 +3214,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3237,10 +3234,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3248,19 +3245,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3277,10 +3274,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3297,10 +3294,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3317,10 +3314,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3337,10 +3334,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3357,10 +3354,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3377,10 +3374,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3397,10 +3394,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3417,10 +3414,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3428,19 +3425,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3457,10 +3454,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3477,10 +3474,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3497,10 +3494,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3517,10 +3514,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3537,10 +3534,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3557,13 +3554,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3577,13 +3574,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3597,10 +3594,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3617,10 +3614,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3628,19 +3625,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3657,10 +3654,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3677,10 +3674,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3697,10 +3694,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3717,10 +3714,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3737,10 +3734,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3757,10 +3754,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3777,10 +3774,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3788,19 +3785,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3817,13 +3814,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3837,13 +3834,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3857,10 +3854,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>9</v>
@@ -3877,53 +3874,53 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>9</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>275</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3937,30 +3934,30 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>43</v>
+        <v>158</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>278</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3968,22 +3965,22 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>282</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3997,130 +3994,130 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>285</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>192</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B132" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>275</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>9</v>
+        <v>278</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>282</v>
+        <v>96</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4128,19 +4125,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4148,19 +4145,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4168,19 +4165,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4188,59 +4185,59 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4248,59 +4245,59 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>275</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4308,19 +4305,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4328,19 +4325,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4348,19 +4345,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4368,19 +4365,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>46</v>
+        <v>158</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4388,19 +4385,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4408,41 +4405,21 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F152" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="336">
   <si>
     <t/>
   </si>
@@ -100,226 +100,271 @@
     <t>CHOKI CHOKI 6X4G</t>
   </si>
   <si>
+    <t>10000322</t>
+  </si>
+  <si>
+    <t>CHOKI CHOKI CHO 4X9G</t>
+  </si>
+  <si>
+    <t>20141002</t>
+  </si>
+  <si>
+    <t>WONHAE MTCHA BRY 30G</t>
+  </si>
+  <si>
+    <t>20139890</t>
+  </si>
+  <si>
+    <t>WNHAE STRW CHEESCAKE</t>
+  </si>
+  <si>
+    <t>20139889</t>
+  </si>
+  <si>
+    <t>WNHAE PISTACHIO CHOC</t>
+  </si>
+  <si>
+    <t>20135198</t>
+  </si>
+  <si>
+    <t>WONHAE YOG.GUM ORI48</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20135661</t>
+  </si>
+  <si>
+    <t>WNHAE GMMY MXD.FRT32</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20033392</t>
+  </si>
+  <si>
+    <t>DELFI CHACHA MINIS25</t>
+  </si>
+  <si>
+    <t>20077110</t>
+  </si>
+  <si>
+    <t>CHACHA MINIS HATS 25</t>
+  </si>
+  <si>
+    <t>20122057</t>
+  </si>
+  <si>
+    <t>CHACHA MINIS CAR12.5</t>
+  </si>
+  <si>
+    <t>20140016</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHO PEANUT 37G</t>
+  </si>
+  <si>
+    <t>20140013</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHOC CRSPY 30G</t>
+  </si>
+  <si>
+    <t>20129814</t>
+  </si>
+  <si>
+    <t>MLKITA CNDY BTES 24G</t>
+  </si>
+  <si>
+    <t>20140908</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD STRW 85G</t>
+  </si>
+  <si>
+    <t>20140907</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD MILK 85G</t>
+  </si>
+  <si>
+    <t>20045175</t>
+  </si>
+  <si>
+    <t>CHA CHA MILK CHO 20G</t>
+  </si>
+  <si>
+    <t>20142588</t>
+  </si>
+  <si>
+    <t>CHA CHA PNUT CHO2X35</t>
+  </si>
+  <si>
+    <t>20063093</t>
+  </si>
+  <si>
+    <t>DELFI MALTITOS 26</t>
+  </si>
+  <si>
+    <t>10000418</t>
+  </si>
+  <si>
+    <t>DELFI CHIC CHOC 36G</t>
+  </si>
+  <si>
+    <t>20024539</t>
+  </si>
+  <si>
+    <t>S/Q BITES ALMOND 30G</t>
+  </si>
+  <si>
+    <t>20136282</t>
+  </si>
+  <si>
+    <t>MILKITA LOLIPOP 3'S</t>
+  </si>
+  <si>
+    <t>20140906</t>
+  </si>
+  <si>
+    <t>MILKITA BAR CHOC 15G</t>
+  </si>
+  <si>
+    <t>20140412</t>
+  </si>
+  <si>
+    <t>MILKITA MILKY BAR 15</t>
+  </si>
+  <si>
+    <t>20113490</t>
+  </si>
+  <si>
+    <t>BENG-BENG ALMOND 35G</t>
+  </si>
+  <si>
+    <t>20044008</t>
+  </si>
+  <si>
+    <t>BENG-BENG MAXX 32G</t>
+  </si>
+  <si>
+    <t>20117108</t>
+  </si>
+  <si>
+    <t>BENG-BENG PCK 3X20G</t>
+  </si>
+  <si>
+    <t>20045176</t>
+  </si>
+  <si>
+    <t>CHA CHA PNUT CHO 20G</t>
+  </si>
+  <si>
+    <t>20112348</t>
+  </si>
+  <si>
+    <t>IDM BLUEBRY D.CHO 45</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20085730</t>
+  </si>
+  <si>
+    <t>IDM CASH MILK CHO 40</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20093638</t>
+  </si>
+  <si>
+    <t>IDM BISC MILK CHO 40</t>
+  </si>
+  <si>
     <t>20128815</t>
   </si>
   <si>
     <t>IDM GUMMY CHO MF 40G</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10000322</t>
-  </si>
-  <si>
-    <t>CHOKI CHOKI CHO 4X9G</t>
-  </si>
-  <si>
-    <t>20141002</t>
-  </si>
-  <si>
-    <t>WONHAE MTCHA BRY 30G</t>
-  </si>
-  <si>
-    <t>20139890</t>
-  </si>
-  <si>
-    <t>WNHAE STRW CHEESCAKE</t>
-  </si>
-  <si>
-    <t>20139889</t>
-  </si>
-  <si>
-    <t>WNHAE PISTACHIO CHOC</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20135198</t>
-  </si>
-  <si>
-    <t>WONHAE YOG.GUM ORI48</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20135661</t>
-  </si>
-  <si>
-    <t>WNHAE GMMY MXD.FRT32</t>
+    <t>20084899</t>
+  </si>
+  <si>
+    <t>L`AGIE GLDN CITY 75G</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20065363</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCOLAT 70</t>
+  </si>
+  <si>
+    <t>20046198</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCOLAT 51</t>
+  </si>
+  <si>
+    <t>20011878</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCO 35G</t>
+  </si>
+  <si>
+    <t>20142589</t>
+  </si>
+  <si>
+    <t>DELFI NOCKER BDD2X35</t>
+  </si>
+  <si>
+    <t>20142997</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCO FB</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20033392</t>
-  </si>
-  <si>
-    <t>DELFI CHACHA MINIS25</t>
-  </si>
-  <si>
-    <t>20077110</t>
-  </si>
-  <si>
-    <t>CHACHA MINIS HATS 25</t>
-  </si>
-  <si>
-    <t>20122057</t>
-  </si>
-  <si>
-    <t>CHACHA MINIS CAR12.5</t>
-  </si>
-  <si>
-    <t>20140016</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHO PEANUT 37G</t>
-  </si>
-  <si>
-    <t>20140013</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHOC CRSPY 30G</t>
-  </si>
-  <si>
-    <t>20129814</t>
-  </si>
-  <si>
-    <t>MLKITA CNDY BTES 24G</t>
-  </si>
-  <si>
-    <t>20140908</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD STRW 85G</t>
-  </si>
-  <si>
-    <t>20140907</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD MILK 85G</t>
-  </si>
-  <si>
-    <t>20045175</t>
-  </si>
-  <si>
-    <t>CHA CHA MILK CHO 20G</t>
-  </si>
-  <si>
-    <t>20142588</t>
-  </si>
-  <si>
-    <t>CHA CHA PNUT CHO2X35</t>
-  </si>
-  <si>
-    <t>20045176</t>
-  </si>
-  <si>
-    <t>CHA CHA PNUT CHO 20G</t>
-  </si>
-  <si>
-    <t>20063093</t>
-  </si>
-  <si>
-    <t>DELFI MALTITOS 26</t>
-  </si>
-  <si>
-    <t>10000418</t>
-  </si>
-  <si>
-    <t>DELFI CHIC CHOC 36G</t>
-  </si>
-  <si>
-    <t>20024539</t>
-  </si>
-  <si>
-    <t>S/Q BITES ALMOND 30G</t>
-  </si>
-  <si>
-    <t>20140906</t>
-  </si>
-  <si>
-    <t>MILKITA BAR CHOC 15G</t>
-  </si>
-  <si>
-    <t>20140412</t>
-  </si>
-  <si>
-    <t>MILKITA MILKY BAR 15</t>
-  </si>
-  <si>
-    <t>20142589</t>
-  </si>
-  <si>
-    <t>DELFI NOCKER BDD2X35</t>
-  </si>
-  <si>
-    <t>20113490</t>
-  </si>
-  <si>
-    <t>BENG-BENG ALMOND 35G</t>
-  </si>
-  <si>
-    <t>20044008</t>
-  </si>
-  <si>
-    <t>BENG-BENG MAXX 32G</t>
-  </si>
-  <si>
-    <t>20117108</t>
-  </si>
-  <si>
-    <t>BENG-BENG PCK 3X20G</t>
-  </si>
-  <si>
-    <t>20112348</t>
-  </si>
-  <si>
-    <t>IDM BLUEBRY D.CHO 45</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20085730</t>
-  </si>
-  <si>
-    <t>IDM CASH MILK CHO 40</t>
-  </si>
-  <si>
-    <t>20093638</t>
-  </si>
-  <si>
-    <t>IDM BISC MILK CHO 40</t>
-  </si>
-  <si>
-    <t>20084899</t>
-  </si>
-  <si>
-    <t>L`AGIE GLDN CITY 75G</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20065363</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCOLAT 70</t>
-  </si>
-  <si>
-    <t>20046198</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCOLAT 51</t>
-  </si>
-  <si>
-    <t>20011878</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCO 35G</t>
+    <t>20142332</t>
+  </si>
+  <si>
+    <t>LARIST CHOCO EGG 20G</t>
+  </si>
+  <si>
+    <t>20120946</t>
+  </si>
+  <si>
+    <t>KINDER JOY DC COMICS</t>
+  </si>
+  <si>
+    <t>20130547</t>
+  </si>
+  <si>
+    <t>DELFI CHOCO DM 2X25G</t>
+  </si>
+  <si>
+    <t>20134029</t>
+  </si>
+  <si>
+    <t>DELFI TRSURE MLK2X30</t>
+  </si>
+  <si>
+    <t>10008315</t>
+  </si>
+  <si>
+    <t>KINDER BUENO CHO 43G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
   </si>
   <si>
     <t>20139949</t>
@@ -328,43 +373,16 @@
     <t>LMNILO CRNCHY CHO 18</t>
   </si>
   <si>
-    <t>20120946</t>
-  </si>
-  <si>
-    <t>KINDER JOY DC COMICS</t>
-  </si>
-  <si>
-    <t>20142332</t>
-  </si>
-  <si>
-    <t>LARIST CHOCO EGG 20G</t>
-  </si>
-  <si>
-    <t>20130547</t>
-  </si>
-  <si>
-    <t>DELFI CHOCO DM 2X25G</t>
-  </si>
-  <si>
-    <t>20134029</t>
-  </si>
-  <si>
-    <t>DELFI TRSURE MLK2X30</t>
-  </si>
-  <si>
     <t>10000757</t>
   </si>
   <si>
     <t>L'AGIE FULL MILK 60G</t>
   </si>
   <si>
-    <t>10008315</t>
-  </si>
-  <si>
-    <t>KINDER BUENO CHO 43G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
+    <t>20142508</t>
+  </si>
+  <si>
+    <t>DARK WONDER  BDD2X40</t>
   </si>
   <si>
     <t>20062877</t>
@@ -391,12 +409,6 @@
     <t>CADBURY CSHW NUT 85G</t>
   </si>
   <si>
-    <t>20142508</t>
-  </si>
-  <si>
-    <t>DARK WONDER  BDD2X40</t>
-  </si>
-  <si>
     <t>20008798</t>
   </si>
   <si>
@@ -406,7 +418,13 @@
     <t>10036987</t>
   </si>
   <si>
-    <t>S/Q CHOCO CASHW 52 G</t>
+    <t>S/Q CHOCO CASHEW 52G</t>
+  </si>
+  <si>
+    <t>20124902</t>
+  </si>
+  <si>
+    <t>SQ B2G1 CASHEW 3X52G</t>
   </si>
   <si>
     <t>20092545</t>
@@ -445,30 +463,30 @@
     <t>MILO CHOCO CUBE67.5G</t>
   </si>
   <si>
+    <t>20129562</t>
+  </si>
+  <si>
+    <t>IDM FD STRW CHOC 45G</t>
+  </si>
+  <si>
+    <t>20129561</t>
+  </si>
+  <si>
+    <t>IDM RAISIN CHOCO 60G</t>
+  </si>
+  <si>
+    <t>20129559</t>
+  </si>
+  <si>
+    <t>IDM ALMND CHOCO 60G</t>
+  </si>
+  <si>
     <t>20129560</t>
   </si>
   <si>
     <t>IDM HAZEL CHOCO 60G</t>
   </si>
   <si>
-    <t>20129562</t>
-  </si>
-  <si>
-    <t>IDM FD STRW CHOC 45G</t>
-  </si>
-  <si>
-    <t>20129561</t>
-  </si>
-  <si>
-    <t>IDM RAISIN CHOCO 60G</t>
-  </si>
-  <si>
-    <t>20129559</t>
-  </si>
-  <si>
-    <t>IDM ALMND CHOCO 60G</t>
-  </si>
-  <si>
     <t>20093135</t>
   </si>
   <si>
@@ -577,10 +595,10 @@
     <t>MINTZ CNDY.PPRMNT 99</t>
   </si>
   <si>
-    <t>20136282</t>
-  </si>
-  <si>
-    <t>MILKITA LOLIPOP 3'S</t>
+    <t>20143054</t>
+  </si>
+  <si>
+    <t>FOXS GUM EMOTIS 50</t>
   </si>
   <si>
     <t>13</t>
@@ -616,61 +634,76 @@
     <t>YUPI KISS STRAW 110G</t>
   </si>
   <si>
+    <t>20141954</t>
+  </si>
+  <si>
+    <t>YUPI CRUNCY GUMMY 50</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20141597</t>
+  </si>
+  <si>
+    <t>FRUZZ GUMMY ASORTD36</t>
+  </si>
+  <si>
+    <t>20142223</t>
+  </si>
+  <si>
+    <t>BONCHA CND GUMMY 60G</t>
+  </si>
+  <si>
+    <t>20138897</t>
+  </si>
+  <si>
+    <t>JLO FRIED EGG 78G</t>
+  </si>
+  <si>
+    <t>20129720</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY WLD SFR44</t>
+  </si>
+  <si>
+    <t>10000312</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY GL.STK 45</t>
+  </si>
+  <si>
+    <t>10006540</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY BB.BEAR45</t>
+  </si>
+  <si>
+    <t>10006534</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY KS.STW 45</t>
+  </si>
+  <si>
+    <t>20064920</t>
+  </si>
+  <si>
+    <t>YUPI LITTLE STARS 45</t>
+  </si>
+  <si>
     <t>20140015</t>
   </si>
   <si>
     <t>AMOS BANANA GUMMY 68</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20141954</t>
-  </si>
-  <si>
-    <t>YUPI CRUNCY GUMMY 50</t>
-  </si>
-  <si>
-    <t>20141597</t>
-  </si>
-  <si>
-    <t>FRUZZ GUMMY ASORTD36</t>
-  </si>
-  <si>
-    <t>20142223</t>
-  </si>
-  <si>
-    <t>BONCHA CND GUMMY 60G</t>
-  </si>
-  <si>
-    <t>20138897</t>
-  </si>
-  <si>
-    <t>JLO FRIED EGG 78G</t>
-  </si>
-  <si>
-    <t>20129720</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY WLD SFR44</t>
-  </si>
-  <si>
-    <t>10000312</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY GL.STK 45</t>
-  </si>
-  <si>
-    <t>10006540</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY BB.BEAR45</t>
-  </si>
-  <si>
-    <t>20064920</t>
-  </si>
-  <si>
-    <t>YUPI LITTLE STARS 45</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20087289</t>
+  </si>
+  <si>
+    <t>CHP.CHUPS BITES 56G</t>
   </si>
   <si>
     <t>20139394</t>
@@ -679,19 +712,40 @@
     <t>JLO GUMMY BEAR 40G</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>20135995</t>
   </si>
   <si>
     <t>JLO GUMMY BITE 40G</t>
   </si>
   <si>
-    <t>20087289</t>
-  </si>
-  <si>
-    <t>CHP.CHUPS BITES 56G</t>
+    <t>20047250</t>
+  </si>
+  <si>
+    <t>YUPI CALCI BEAN 70G</t>
+  </si>
+  <si>
+    <t>20080530</t>
+  </si>
+  <si>
+    <t>YUPI BIG BURGER 32G</t>
+  </si>
+  <si>
+    <t>20048724</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY PIZZA 23G</t>
+  </si>
+  <si>
+    <t>20136191</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY NOODLE23G</t>
+  </si>
+  <si>
+    <t>20052776</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY B/FRNK 32</t>
   </si>
   <si>
     <t>20139774</t>
@@ -700,42 +754,6 @@
     <t>CH.CHUP ROPES S/C 24</t>
   </si>
   <si>
-    <t>10006534</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY KS.STW 45</t>
-  </si>
-  <si>
-    <t>20080530</t>
-  </si>
-  <si>
-    <t>YUPI BIG BURGER 32G</t>
-  </si>
-  <si>
-    <t>20048724</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY PIZZA 23G</t>
-  </si>
-  <si>
-    <t>20136191</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY NOODLE23G</t>
-  </si>
-  <si>
-    <t>20052776</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY B/FRNK 32</t>
-  </si>
-  <si>
-    <t>20047250</t>
-  </si>
-  <si>
-    <t>YUPI CALCI BEAN 70G</t>
-  </si>
-  <si>
     <t>20138164</t>
   </si>
   <si>
@@ -802,6 +820,15 @@
     <t>SUGUS STICK BLCRNT30</t>
   </si>
   <si>
+    <t>20129719</t>
+  </si>
+  <si>
+    <t>FROZZ ANGGR MINT 14G</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
     <t>20014081</t>
   </si>
   <si>
@@ -860,15 +887,6 @@
   </si>
   <si>
     <t>MILTON PSTLS LMN16.5</t>
-  </si>
-  <si>
-    <t>20129719</t>
-  </si>
-  <si>
-    <t>FROZZ ANGGR MINT 14G</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
   </si>
   <si>
     <t>10011038</t>
@@ -1393,7 +1411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1620,15 +1638,15 @@
         <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1645,10 +1663,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1665,10 +1683,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1685,10 +1703,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1697,7 +1715,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1705,10 +1723,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1717,7 +1735,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1725,19 +1743,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1745,10 +1763,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1757,7 +1775,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1765,10 +1783,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1777,7 +1795,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1785,10 +1803,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1797,7 +1815,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1805,10 +1823,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1817,7 +1835,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1825,10 +1843,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1837,7 +1855,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1845,10 +1863,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1857,7 +1875,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1865,10 +1883,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1877,7 +1895,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1885,19 +1903,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1905,10 +1923,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1917,7 +1935,7 @@
         <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1925,10 +1943,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1937,7 +1955,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1945,10 +1963,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1957,7 +1975,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1965,10 +1983,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1977,7 +1995,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1985,10 +2003,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1997,7 +2015,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2005,19 +2023,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2025,10 +2043,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -2037,7 +2055,7 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2045,10 +2063,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2057,7 +2075,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2065,10 +2083,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2077,7 +2095,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2085,10 +2103,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2097,7 +2115,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2105,10 +2123,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2117,7 +2135,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2125,30 +2143,30 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2157,18 +2175,18 @@
         <v>21</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2177,18 +2195,18 @@
         <v>21</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2197,18 +2215,18 @@
         <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2217,18 +2235,18 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2237,7 +2255,7 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2245,10 +2263,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2257,7 +2275,7 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2265,10 +2283,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2277,7 +2295,7 @@
         <v>21</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2285,10 +2303,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2297,7 +2315,7 @@
         <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2305,19 +2323,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2337,10 +2355,10 @@
         <v>24</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2357,7 +2375,7 @@
         <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2377,7 +2395,7 @@
         <v>24</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2397,10 +2415,10 @@
         <v>24</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2417,7 +2435,7 @@
         <v>24</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>117</v>
@@ -2434,10 +2452,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2454,13 +2472,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2474,10 +2492,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2494,10 +2512,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2514,10 +2532,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2534,10 +2552,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2554,10 +2572,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2574,10 +2592,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2594,10 +2612,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2614,10 +2632,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2634,10 +2652,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2654,10 +2672,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2674,10 +2692,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2694,13 +2712,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2714,13 +2732,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2734,13 +2752,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2754,13 +2772,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2774,13 +2792,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2794,13 +2812,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2814,30 +2832,30 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2845,39 +2863,39 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2894,13 +2912,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2914,10 +2932,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2934,10 +2952,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2954,13 +2972,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2974,10 +2992,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2985,19 +3003,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3005,19 +3023,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3025,19 +3043,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3054,10 +3072,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3074,13 +3092,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3094,13 +3112,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3114,10 +3132,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3125,59 +3143,59 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3194,10 +3212,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3214,10 +3232,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3234,10 +3252,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3245,19 +3263,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3265,19 +3283,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3285,19 +3303,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3314,10 +3332,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3334,10 +3352,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3354,10 +3372,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3374,10 +3392,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3394,10 +3412,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3414,10 +3432,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3425,19 +3443,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3445,19 +3463,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3465,19 +3483,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3494,10 +3512,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3514,10 +3532,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3534,10 +3552,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3554,13 +3572,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3574,10 +3592,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3594,10 +3612,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3614,30 +3632,30 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3645,19 +3663,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3665,19 +3683,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3694,10 +3712,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3714,10 +3732,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3734,10 +3752,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3754,10 +3772,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3774,10 +3792,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3785,19 +3803,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3805,42 +3823,42 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3854,13 +3872,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3874,10 +3892,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>271</v>
@@ -3894,13 +3912,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3914,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3934,33 +3952,33 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>278</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3974,10 +3992,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3994,93 +4012,93 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>285</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>278</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>96</v>
+        <v>280</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4094,13 +4112,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4114,13 +4132,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>5</v>
+        <v>287</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4134,13 +4152,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4154,10 +4172,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4174,10 +4192,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4185,39 +4203,39 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4225,19 +4243,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4254,13 +4272,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>271</v>
+        <v>88</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4274,10 +4292,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4294,10 +4312,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4314,13 +4332,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>280</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4334,10 +4352,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4354,10 +4372,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4374,10 +4392,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4394,10 +4412,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4414,12 +4432,72 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="F151" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="343">
   <si>
     <t/>
   </si>
@@ -94,6 +94,15 @@
     <t>CHA CHA SURPRISE 2'S</t>
   </si>
   <si>
+    <t>20143070</t>
+  </si>
+  <si>
+    <t>CHA CHA TSUM 2X12.5</t>
+  </si>
+  <si>
+    <t>TG,(E-1B)</t>
+  </si>
+  <si>
     <t>20097984</t>
   </si>
   <si>
@@ -142,6 +151,15 @@
     <t>9</t>
   </si>
   <si>
+    <t>20143073</t>
+  </si>
+  <si>
+    <t>HIFRT GREN GRP PCK25</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20033392</t>
   </si>
   <si>
@@ -160,6 +178,12 @@
     <t>CHACHA MINIS CAR12.5</t>
   </si>
   <si>
+    <t>20143071</t>
+  </si>
+  <si>
+    <t>CHA CHA DISNEY 25</t>
+  </si>
+  <si>
     <t>20140016</t>
   </si>
   <si>
@@ -329,9 +353,6 @@
   </si>
   <si>
     <t>SNICKERS CHOCO FB</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>20142332</t>
@@ -1411,7 +1432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1615,18 +1636,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1635,7 +1656,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1643,10 +1664,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1655,7 +1676,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1663,10 +1684,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1675,7 +1696,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1683,10 +1704,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1695,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1703,10 +1724,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1715,7 +1736,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1752,10 +1773,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1763,19 +1784,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1783,10 +1804,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1795,7 +1816,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1803,10 +1824,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1815,7 +1836,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1823,10 +1844,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1835,7 +1856,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1843,10 +1864,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1855,7 +1876,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1863,10 +1884,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1875,7 +1896,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1883,10 +1904,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1895,7 +1916,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1903,19 +1924,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1923,19 +1944,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1943,19 +1964,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1963,10 +1984,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1975,7 +1996,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1983,10 +2004,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1995,7 +2016,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2003,10 +2024,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2015,7 +2036,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2023,19 +2044,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2043,19 +2064,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2063,19 +2084,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2083,10 +2104,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2095,7 +2116,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2103,10 +2124,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2115,7 +2136,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2123,10 +2144,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2135,7 +2156,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2143,42 +2164,42 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2192,13 +2213,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2215,18 +2236,18 @@
         <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2235,18 +2256,18 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2255,18 +2276,18 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2275,18 +2296,18 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2295,18 +2316,18 @@
         <v>21</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2315,7 +2336,7 @@
         <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2323,10 +2344,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2335,7 +2356,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2343,39 +2364,39 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2383,19 +2404,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2403,10 +2424,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2415,18 +2436,18 @@
         <v>24</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2435,10 +2456,10 @@
         <v>24</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2455,7 +2476,7 @@
         <v>24</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2472,13 +2493,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,30 +2513,30 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2523,39 +2544,39 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2563,19 +2584,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2583,10 +2604,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2595,7 +2616,7 @@
         <v>42</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2603,10 +2624,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2615,7 +2636,7 @@
         <v>42</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2623,10 +2644,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2635,7 +2656,7 @@
         <v>42</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2643,19 +2664,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2663,19 +2684,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2683,19 +2704,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2703,19 +2724,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2723,19 +2744,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2743,19 +2764,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2763,142 +2784,142 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>164</v>
+        <v>42</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2912,10 +2933,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2932,13 +2953,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2952,10 +2973,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2963,39 +2984,39 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3003,19 +3024,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3023,39 +3044,39 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3072,10 +3093,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3092,10 +3113,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3112,10 +3133,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3123,19 +3144,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3143,59 +3164,59 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3212,13 +3233,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3232,13 +3253,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3252,10 +3273,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3263,19 +3284,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3283,19 +3304,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3303,19 +3324,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3332,10 +3353,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3352,10 +3373,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3372,10 +3393,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3383,19 +3404,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3403,19 +3424,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3423,19 +3444,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3443,19 +3464,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3463,19 +3484,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3483,19 +3504,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3512,10 +3533,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3532,10 +3553,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3552,10 +3573,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3563,19 +3584,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3583,19 +3604,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3603,19 +3624,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3623,39 +3644,39 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3663,19 +3684,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3683,22 +3704,22 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3712,10 +3733,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3732,10 +3753,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3752,10 +3773,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3763,19 +3784,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3783,19 +3804,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3803,19 +3824,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3823,19 +3844,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3843,19 +3864,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3872,10 +3893,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3892,33 +3913,33 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>271</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3932,13 +3953,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3952,33 +3973,33 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>9</v>
+        <v>278</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>280</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3992,13 +4013,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4012,13 +4033,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4032,10 +4053,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>164</v>
+        <v>42</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>287</v>
@@ -4052,10 +4073,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4072,10 +4093,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>196</v>
+        <v>48</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4092,13 +4113,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4112,13 +4133,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4132,13 +4153,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>203</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>287</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4152,90 +4173,90 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>95</v>
+        <v>287</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4243,19 +4264,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4272,13 +4293,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4292,10 +4313,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4312,10 +4333,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4323,39 +4344,39 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>280</v>
+        <v>96</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4363,19 +4384,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4383,39 +4404,39 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>287</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4423,19 +4444,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4443,19 +4464,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>164</v>
+        <v>42</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4463,19 +4484,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4483,21 +4504,81 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>196</v>
+        <v>48</v>
       </c>
       <c r="F154" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F157" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -214,6 +214,12 @@
     <t>MLKITA PUDD MILK 85G</t>
   </si>
   <si>
+    <t>20136282</t>
+  </si>
+  <si>
+    <t>MILKITA LOLIPOP 3'S</t>
+  </si>
+  <si>
     <t>20045175</t>
   </si>
   <si>
@@ -244,12 +250,6 @@
     <t>S/Q BITES ALMOND 30G</t>
   </si>
   <si>
-    <t>20136282</t>
-  </si>
-  <si>
-    <t>MILKITA LOLIPOP 3'S</t>
-  </si>
-  <si>
     <t>20140906</t>
   </si>
   <si>
@@ -343,16 +343,16 @@
     <t>SNICKERS CHOCO 35G</t>
   </si>
   <si>
+    <t>20142997</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCO FB</t>
+  </si>
+  <si>
     <t>20142589</t>
   </si>
   <si>
     <t>DELFI NOCKER BDD2X35</t>
-  </si>
-  <si>
-    <t>20142997</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCO FB</t>
   </si>
   <si>
     <t>20142332</t>
@@ -1993,10 +1993,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2016,7 +2016,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2036,7 +2036,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2056,7 +2056,7 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2076,7 +2076,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2096,7 +2096,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -3576,7 +3576,7 @@
         <v>235</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3596,7 +3596,7 @@
         <v>235</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3616,7 +3616,7 @@
         <v>235</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3636,7 +3636,7 @@
         <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3656,7 +3656,7 @@
         <v>235</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3676,7 +3676,7 @@
         <v>235</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3696,7 +3696,7 @@
         <v>235</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3716,7 +3716,7 @@
         <v>235</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>103</v>
@@ -3736,7 +3736,7 @@
         <v>235</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3756,7 +3756,7 @@
         <v>235</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3996,7 +3996,7 @@
         <v>273</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>9</v>
@@ -4016,7 +4016,7 @@
         <v>273</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>9</v>
@@ -4036,7 +4036,7 @@
         <v>273</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>9</v>
@@ -4056,7 +4056,7 @@
         <v>273</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>287</v>
@@ -4076,7 +4076,7 @@
         <v>273</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4096,7 +4096,7 @@
         <v>273</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4116,7 +4116,7 @@
         <v>273</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>294</v>
@@ -4136,7 +4136,7 @@
         <v>273</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4156,7 +4156,7 @@
         <v>273</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4176,7 +4176,7 @@
         <v>301</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>287</v>
@@ -4196,7 +4196,7 @@
         <v>301</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>9</v>
@@ -4216,7 +4216,7 @@
         <v>301</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>294</v>
@@ -4236,7 +4236,7 @@
         <v>301</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>103</v>
@@ -4256,7 +4256,7 @@
         <v>301</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4276,7 +4276,7 @@
         <v>301</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4296,7 +4296,7 @@
         <v>301</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4316,7 +4316,7 @@
         <v>301</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="346">
   <si>
     <t/>
   </si>
@@ -100,9 +100,6 @@
     <t>CHA CHA TSUM 2X12.5</t>
   </si>
   <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
     <t>20097984</t>
   </si>
   <si>
@@ -160,6 +157,15 @@
     <t>10</t>
   </si>
   <si>
+    <t>20143332</t>
+  </si>
+  <si>
+    <t>HIFRUIT GRAPE  25G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>20033392</t>
   </si>
   <si>
@@ -526,9 +532,6 @@
     <t>KALPA SHRE IT 90G</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>20053360</t>
   </si>
   <si>
@@ -712,13 +715,19 @@
     <t>YUPI LITTLE STARS 45</t>
   </si>
   <si>
+    <t>20143286</t>
+  </si>
+  <si>
+    <t>AMOS MANGO PEELZ PCH</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>20140015</t>
   </si>
   <si>
     <t>AMOS BANANA GUMMY 68</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>20087289</t>
@@ -1432,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1639,15 +1648,15 @@
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1664,10 +1673,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1684,10 +1693,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1704,10 +1713,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1724,10 +1733,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1744,10 +1753,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1756,7 +1765,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1764,10 +1773,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1776,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1784,10 +1793,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1796,7 +1805,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1804,19 +1813,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1836,7 +1845,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1856,7 +1865,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1876,7 +1885,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1896,7 +1905,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1916,7 +1925,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1936,7 +1945,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1956,7 +1965,7 @@
         <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1976,7 +1985,7 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1996,7 +2005,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2013,10 +2022,10 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2036,7 +2045,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2056,7 +2065,7 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2076,7 +2085,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2096,7 +2105,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2113,10 +2122,10 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2136,7 +2145,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2156,7 +2165,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2176,7 +2185,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2196,7 +2205,7 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2216,7 +2225,7 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2233,21 +2242,21 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F40" s="1" t="s">
-        <v>93</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2256,18 +2265,18 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2276,10 +2285,10 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2296,10 +2305,10 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2316,18 +2325,18 @@
         <v>21</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2336,10 +2345,10 @@
         <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2356,7 +2365,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2376,7 +2385,7 @@
         <v>21</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2396,7 +2405,7 @@
         <v>21</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2416,7 +2425,7 @@
         <v>21</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2433,13 +2442,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2456,10 +2465,10 @@
         <v>24</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2476,7 +2485,7 @@
         <v>24</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2496,7 +2505,7 @@
         <v>24</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2516,18 +2525,18 @@
         <v>24</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2536,10 +2545,10 @@
         <v>24</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2553,13 +2562,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2573,13 +2582,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2593,10 +2602,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2613,10 +2622,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2633,10 +2642,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2653,10 +2662,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2673,10 +2682,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2693,10 +2702,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2713,10 +2722,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2733,10 +2742,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2753,10 +2762,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2773,10 +2782,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2793,10 +2802,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2813,10 +2822,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2833,10 +2842,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2853,13 +2862,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2873,13 +2882,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2893,13 +2902,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2913,13 +2922,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2933,13 +2942,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2953,13 +2962,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2973,30 +2982,30 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3004,19 +3013,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3024,19 +3033,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3044,59 +3053,59 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3104,19 +3113,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3124,19 +3133,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3144,19 +3153,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3164,19 +3173,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3184,19 +3193,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3204,19 +3213,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3224,39 +3233,39 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>9</v>
@@ -3264,39 +3273,39 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3304,19 +3313,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3324,19 +3333,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3344,19 +3353,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3364,19 +3373,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3384,19 +3393,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3404,19 +3413,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3424,19 +3433,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3444,19 +3453,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3464,19 +3473,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3484,19 +3493,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3504,19 +3513,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3524,19 +3533,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3544,19 +3553,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3564,19 +3573,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3584,19 +3593,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3604,19 +3613,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3624,19 +3633,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3644,19 +3653,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3664,19 +3673,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3684,19 +3693,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3704,39 +3713,39 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3744,39 +3753,39 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3784,19 +3793,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3804,19 +3813,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3824,19 +3833,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3844,19 +3853,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3864,19 +3873,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3884,19 +3893,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3904,19 +3913,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3924,19 +3933,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3944,19 +3953,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3964,79 +3973,79 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>278</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>9</v>
@@ -4044,99 +4053,99 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>287</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4144,159 +4153,159 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>287</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>297</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4304,19 +4313,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4324,19 +4333,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4344,39 +4353,39 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4384,59 +4393,59 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>287</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4444,39 +4453,39 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4484,19 +4493,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4504,19 +4513,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4524,19 +4533,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4544,19 +4553,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4564,21 +4573,61 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F157" s="1" t="s">
+      <c r="B158" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F159" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -619,15 +619,21 @@
     <t>MINTZ CNDY.PPRMNT 99</t>
   </si>
   <si>
+    <t>20143521</t>
+  </si>
+  <si>
+    <t>RJN BRY SWEET CDY 40</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>20143054</t>
   </si>
   <si>
     <t>FOXS GUM EMOTIS 50</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>20142221</t>
   </si>
   <si>
@@ -718,16 +724,10 @@
     <t>20143286</t>
   </si>
   <si>
-    <t>AMOS MANGO PEELZ PCH</t>
+    <t>AMOS PEELZ MANGO 65G</t>
   </si>
   <si>
     <t>15</t>
-  </si>
-  <si>
-    <t>20140015</t>
-  </si>
-  <si>
-    <t>AMOS BANANA GUMMY 68</t>
   </si>
   <si>
     <t>20087289</t>
@@ -3422,10 +3422,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3433,19 +3433,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3462,10 +3462,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3482,10 +3482,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3502,10 +3502,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3522,10 +3522,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3542,10 +3542,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3562,10 +3562,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3582,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3602,10 +3602,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3613,19 +3613,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3642,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>12</v>
@@ -3662,7 +3662,7 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>15</v>
@@ -3682,7 +3682,7 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>18</v>
@@ -3702,7 +3702,7 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>21</v>
@@ -3722,7 +3722,7 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>24</v>
@@ -3742,7 +3742,7 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>41</v>
@@ -3762,7 +3762,7 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>44</v>
@@ -3782,7 +3782,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>47</v>
@@ -3802,7 +3802,7 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>50</v>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="342">
   <si>
     <t/>
   </si>
@@ -286,12 +286,6 @@
     <t>BENG-BENG PCK 3X20G</t>
   </si>
   <si>
-    <t>20045176</t>
-  </si>
-  <si>
-    <t>CHA CHA PNUT CHO 20G</t>
-  </si>
-  <si>
     <t>20112348</t>
   </si>
   <si>
@@ -956,12 +950,6 @@
   </si>
   <si>
     <t>KOPIKO CANDY PCK 8'S</t>
-  </si>
-  <si>
-    <t>20140413</t>
-  </si>
-  <si>
-    <t>SUPER ZUPER  PCK 5S</t>
   </si>
   <si>
     <t>20138030</t>
@@ -1441,7 +1429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2242,21 +2230,21 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2265,18 +2253,18 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2285,10 +2273,10 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2305,10 +2293,10 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2325,18 +2313,18 @@
         <v>21</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2345,10 +2333,10 @@
         <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2365,7 +2353,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2385,7 +2373,7 @@
         <v>21</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2405,7 +2393,7 @@
         <v>21</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2425,7 +2413,7 @@
         <v>21</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2442,13 +2430,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2465,10 +2453,10 @@
         <v>24</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2485,7 +2473,7 @@
         <v>24</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2505,7 +2493,7 @@
         <v>24</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2525,18 +2513,18 @@
         <v>24</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2545,10 +2533,10 @@
         <v>24</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>126</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2562,13 +2550,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2585,10 +2573,10 @@
         <v>41</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2605,7 +2593,7 @@
         <v>41</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2625,7 +2613,7 @@
         <v>41</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2645,7 +2633,7 @@
         <v>41</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2665,7 +2653,7 @@
         <v>41</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2682,10 +2670,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2705,7 +2693,7 @@
         <v>44</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2725,7 +2713,7 @@
         <v>44</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2745,7 +2733,7 @@
         <v>44</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2765,7 +2753,7 @@
         <v>44</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2782,10 +2770,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2805,7 +2793,7 @@
         <v>47</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2825,7 +2813,7 @@
         <v>47</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2845,7 +2833,7 @@
         <v>47</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2865,10 +2853,10 @@
         <v>47</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2885,10 +2873,10 @@
         <v>47</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2905,10 +2893,10 @@
         <v>47</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2925,10 +2913,10 @@
         <v>47</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2945,10 +2933,10 @@
         <v>47</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2965,10 +2953,10 @@
         <v>47</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2985,10 +2973,10 @@
         <v>47</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3002,10 +2990,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3025,7 +3013,7 @@
         <v>50</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3045,7 +3033,7 @@
         <v>50</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3065,10 +3053,10 @@
         <v>50</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3085,10 +3073,10 @@
         <v>50</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3105,7 +3093,7 @@
         <v>50</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3125,7 +3113,7 @@
         <v>50</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3142,10 +3130,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3153,19 +3141,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3182,10 +3170,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3202,10 +3190,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3222,10 +3210,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3242,13 +3230,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3262,10 +3250,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>9</v>
@@ -3282,30 +3270,30 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3322,10 +3310,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3342,10 +3330,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3362,10 +3350,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3382,10 +3370,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3402,10 +3390,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3422,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3433,19 +3421,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3462,10 +3450,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3482,10 +3470,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3502,10 +3490,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3522,10 +3510,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3542,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3562,10 +3550,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3582,10 +3570,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3602,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3613,19 +3601,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3642,10 +3630,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3662,10 +3650,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3682,10 +3670,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3702,10 +3690,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3722,10 +3710,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3742,13 +3730,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3762,13 +3750,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3782,10 +3770,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3802,10 +3790,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3813,19 +3801,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3842,10 +3830,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3862,10 +3850,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3882,10 +3870,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3902,10 +3890,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3922,10 +3910,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3942,10 +3930,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3962,10 +3950,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3973,19 +3961,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4002,33 +3990,33 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>279</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>281</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4042,10 +4030,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>9</v>
@@ -4062,10 +4050,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>9</v>
@@ -4082,33 +4070,33 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>290</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4122,10 +4110,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4142,33 +4130,33 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>295</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>297</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,10 +4170,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4202,33 +4190,33 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>288</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>290</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4242,13 +4230,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>295</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4262,13 +4250,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>297</v>
+        <v>103</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4282,13 +4270,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4302,10 +4290,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4322,10 +4310,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4342,10 +4330,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4353,39 +4341,39 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4402,13 +4390,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4422,13 +4410,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>288</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4442,10 +4430,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4462,13 +4450,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>290</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4482,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4502,10 +4490,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4522,10 +4510,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4542,10 +4530,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4562,10 +4550,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>47</v>
+        <v>187</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4582,52 +4570,12 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F159" s="1" t="s">
         <v>5</v>
       </c>
     </row>
